--- a/processed_ruby_restored_xlsx/sc031_３日目.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc031_３日目.ss.xlsx
@@ -655,9 +655,9 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Even though she was the one who unearthed the Sugoroku
-and must be quietly excited, it’s so like Rin-chan
-that she doesn’t forget her own enjoyment.</t>
+          <t>Even though she was the one who unearthed the
+Sugoroku and must be quietly excited, it’s so like
+Rin-chan that she doesn’t forget her own enjoyment.</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -948,8 +948,8 @@
       <c r="B32" s="1" t="inlineStr">
         <is>
           <t>Right after putting on her teacher act, she
-immediately reverted to the same wide-eyed look as the
-others.</t>
+immediately reverted to the same wide-eyed look as
+the others.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1503,8 +1503,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>「I think you should ask Niini. I'm pretty sure she has
-all the discs...」</t>
+          <t>「I think you should ask Niini. I'm pretty sure she
+has all the discs...」</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1579,8 +1579,8 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Even though it was nothing special, my stock just shot
-up.</t>
+          <t>Even though it was nothing special, my stock just
+shot up.</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1749,8 +1749,8 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's face suddenly brightened, and then she got
-all fired up again.</t>
+          <t>Nono-chan's face suddenly brightened, and then she
+got all fired up again.</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1780,8 +1780,8 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>The X on the map is in the mountains on the way to the
-Gakuen.</t>
+          <t>The X on the map is in the mountains on the way to
+the Gakuen.</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1797,8 +1797,8 @@
       <c r="B87" s="1" t="inlineStr">
         <is>
           <t>It's a small island, but walking that far in the
-girls' shoes would be tough, so we decided to take the
-bus as close as possible.</t>
+girls' shoes would be tough, so we decided to take
+the bus as close as possible.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1874,8 +1874,8 @@
       <c r="B92" s="1" t="inlineStr">
         <is>
           <t>Nono-chan gets in at the front and boards the bus,
-followed by Miru-chan, Rin-chan, and Rurichiyo-chan in
-that order.</t>
+followed by Miru-chan, Rin-chan, and Rurichiyo-chan
+in that order.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2322,8 +2322,8 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>Inside the bus, everyone was staring at the map spread
-out by Nono-chan.</t>
+          <t>Inside the bus, everyone was staring at the map
+spread out by Nono-chan.</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2872,9 +2872,9 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan lines up her thumb and index finger with the
-scale bar, then taps them along the route from the
-dorm to measure the distance.</t>
+          <t>Nono-chan lines up her thumb and index finger with
+the scale bar, then taps them along the route from
+the dorm to measure the distance.</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3200,7 +3200,8 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>...and at that, Miru-chan nodded as if she understood.</t>
+          <t>...and at that, Miru-chan nodded as if she
+understood.</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3338,7 +3339,8 @@
       <c r="B187" s="1" t="inlineStr">
         <is>
           <t>Rurichiyo-chan smiled brightly and praised Nono-chan,
-though she didn't seem intent on saying anything more.</t>
+though she didn't seem intent on saying anything
+more.</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3428,8 +3430,8 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan snapped her finger and pointed, and the spot
-she indicated was just a little ahead of where
+          <t>Nono-chan snapped her finger and pointed, and the
+spot she indicated was just a little ahead of where
 Rurichiyo-chan had pointed.</t>
         </is>
       </c>
@@ -3824,7 +3826,8 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>「Ah... no, I just happened to get it right by chance.」</t>
+          <t>「Ah... no, I just happened to get it right by
+chance.」</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3916,8 +3919,8 @@
       <c r="B225" s="1" t="inlineStr">
         <is>
           <t>「Ahaha... If we'd known how long it would take up to
-this point, it would've matched sensei's calculations,
-though, right？」</t>
+this point, it would've matched sensei's
+calculations, though, right？」</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -4088,8 +4091,8 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan recovered in an instant and this time pulled
-out a compass, holding it up at eye level.</t>
+          <t>Nono-chan recovered in an instant and this time
+pulled out a compass, holding it up at eye level.</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4119,8 +4122,8 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>「I totally know how to read the map！ We'll go straight
-to the X without getting lost！」</t>
+          <t>「I totally know how to read the map！ We'll go
+straight to the X without getting lost！」</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4226,8 +4229,8 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>After getting off the bus, Nono-chan took the lead and
-pushed into the forest.</t>
+          <t>After getting off the bus, Nono-chan took the lead
+and pushed into the forest.</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4242,8 +4245,8 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan seems to know how to read the map, but she's
-heading down a pathless route.</t>
+          <t>Nono-chan seems to know how to read the map, but
+she's heading down a pathless route.</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4320,8 +4323,9 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>Walking while dodging trees makes it easy to lose your
-sense of direction, but at this rate it seems fine.</t>
+          <t>Walking while dodging trees makes it easy to lose
+your sense of direction, but at this rate it seems
+fine.</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4656,8 +4660,8 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>For me, it's worse if she starts crying than if we get
-lost...</t>
+          <t>For me, it's worse if she starts crying than if we
+get lost...</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -5909,8 +5913,8 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>「Well... besides, I was the one who made that sugoroku
-in the first place.」</t>
+          <t>「Well... besides, I was the one who made that
+sugoroku in the first place.」</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -6076,8 +6080,8 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>Eager Miru-chan grabs my backpack and tries to pull it
-down.</t>
+          <t>Eager Miru-chan grabs my backpack and tries to pull
+it down.</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -7118,8 +7122,8 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t>As long as you live on this island, when you’re a kid,
-even if you want one you can’t get it.</t>
+          <t>As long as you live on this island, when you’re a
+kid, even if you want one you can’t get it.</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -7151,8 +7155,8 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>How nostalgic... I treasured it, because I’d racked my
-brains to keep from arousing suspicion.</t>
+          <t>How nostalgic... I treasured it, because I’d racked
+my brains to keep from arousing suspicion.</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -7979,7 +7983,8 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t>「...Or rather, that's not everyone's—it's my book...？」</t>
+          <t>「...Or rather, that's not everyone's—it's my
+book...？」</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -8133,8 +8138,8 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t>But if they'll give it back later, I guess I'll let it
-slide？</t>
+          <t>But if they'll give it back later, I guess I'll let
+it slide？</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -8274,9 +8279,9 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>Even though I was a boy, back when I was a kid I could
-come into the woods too, so it made sense that there'd
-be a path like that.</t>
+          <t>Even though I was a boy, back when I was a kid I
+could come into the woods too, so it made sense that
+there'd be a path like that.</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8582,8 +8587,8 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha！ Eating a bento in a place like this is kind of
-romantic, right？！」</t>
+          <t>「Ahaha！ Eating a bento in a place like this is kind
+of romantic, right？！」</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8782,7 +8787,8 @@
       <c r="B542" s="1" t="inlineStr">
         <is>
           <t>「Ah… everyone, before touching the food, let's make
-sure to properly wipe our hands with wet wipes, okay？」</t>
+sure to properly wipe our hands with wet wipes,
+okay？」</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -8844,8 +8850,8 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan proudly produced the things she had prepared
-in advance.</t>
+          <t>Nono-chan proudly produced the things she had
+prepared in advance.</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -9105,8 +9111,8 @@
       <c r="B563" s="1" t="inlineStr">
         <is>
           <t>I twisted my body to face the direction she was
-pulling me, and Rin-chan, eyes sparkling, was pointing
-somewhere.</t>
+pulling me, and Rin-chan, eyes sparkling, was
+pointing somewhere.</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -9197,8 +9203,8 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>And just behind the nearest tree, a small creature was
-peeking around, looking startled.</t>
+          <t>And just behind the nearest tree, a small creature
+was peeking around, looking startled.</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -10163,8 +10169,8 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. Before, we saw one near the Gakuen together and
-she yelled 'big mouse!' and ran away—」</t>
+          <t>「Yeah. Before, we saw one near the Gakuen together
+and she yelled 'big mouse!' and ran away—」</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -10241,9 +10247,9 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>「Ah, but maybe ferrets would be okay？ Ferrets are pure
-white and cute, and I hear they become really attached
-to people when kept as pets, you know？」</t>
+          <t>「Ah, but maybe ferrets would be okay？ Ferrets are
+pure white and cute, and I hear they become really
+attached to people when kept as pets, you know？」</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10875,8 +10881,8 @@
       <c r="B678" s="1" t="inlineStr">
         <is>
           <t>Even if she had gone into the woods, Rurichiyo-chan
-wouldn’t have gone out of her way to walk into a place
-that’s hard to get through.</t>
+wouldn’t have gone out of her way to walk into a
+place that’s hard to get through.</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -11185,8 +11191,8 @@
       </c>
       <c r="B698" s="1" t="inlineStr">
         <is>
-          <t>Because they were raised by the Arisugawa family, they
-feel reluctant to pee anywhere but a toilet.</t>
+          <t>Because they were raised by the Arisugawa family,
+they feel reluctant to pee anywhere but a toilet.</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -11247,8 +11253,8 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>Even though no one's watching, Rurichiyo-chan is still
-worried about people's eyes.</t>
+          <t>Even though no one's watching, Rurichiyo-chan is
+still worried about people's eyes.</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -11293,8 +11299,8 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>「Since it's my oji-sama, if I notice I'll come looking
-for me, phew...」</t>
+          <t>「Since it's my oji-sama, if I notice I'll come
+looking for me, phew...」</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11324,8 +11330,8 @@
       </c>
       <c r="B707" s="1" t="inlineStr">
         <is>
-          <t>What would my reaction be if I walked out and said I'm
-actually already here...？</t>
+          <t>What would my reaction be if I walked out and said
+I'm actually already here...？</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -11585,8 +11591,8 @@
       <c r="B724" s="1" t="inlineStr">
         <is>
           <t>Also, with her crotch exposed as she crouches, she
-seems to be very sensitive to the sway of the grass on
-the ground.</t>
+seems to be very sensitive to the sway of the grass
+on the ground.</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -11766,8 +11772,9 @@
       </c>
       <c r="B736" s="1" t="inlineStr">
         <is>
-          <t>I was hiding in the shadow of a tree and got startled,
-but Rurichiyo-chan must've been even more shocked.</t>
+          <t>I was hiding in the shadow of a tree and got
+startled, but Rurichiyo-chan must've been even more
+shocked.</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -11919,8 +11926,8 @@
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
-          <t>But that was only for a moment; it quickly melted into
-the tree shadows and ran off.</t>
+          <t>But that was only for a moment; it quickly melted
+into the tree shadows and ran off.</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -11982,8 +11989,8 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>Also, she was too weak to put any strength into it, so
-her cries came out feeble.</t>
+          <t>Also, she was too weak to put any strength into it,
+so her cries came out feeble.</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -12044,8 +12051,8 @@
       </c>
       <c r="B754" s="1" t="inlineStr">
         <is>
-          <t>It's already gone, but being unable to move and scared
-like that had thrown her into a panic.</t>
+          <t>It's already gone, but being unable to move and
+scared like that had thrown her into a panic.</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -12598,8 +12605,8 @@
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>…It's a bit late to say it now, but I'm going to leave
-Rurichiyo-chan alone.</t>
+          <t>…It's a bit late to say it now, but I'm going to
+leave Rurichiyo-chan alone.</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -12843,8 +12850,8 @@
       </c>
       <c r="B806" s="1" t="inlineStr">
         <is>
-          <t>Even as she says no, Rurichiyo-chan lifts her face and
-lets out a sultry sound.</t>
+          <t>Even as she says no, Rurichiyo-chan lifts her face
+and lets out a sultry sound.</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -12859,8 +12866,8 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>The contrast between her cheeks flushed with shame and
-her half-closed, blissful eyes from the urge to
+          <t>The contrast between her cheeks flushed with shame
+and her half-closed, blissful eyes from the urge to
 urinate tells the whole story of Rurichiyo-chan's
 state.</t>
         </is>
@@ -13570,7 +13577,8 @@
       </c>
       <c r="B853" s="1" t="inlineStr">
         <is>
-          <t>She's still in angry mode and even curt with everyone.</t>
+          <t>She's still in angry mode and even curt with
+everyone.</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -13692,9 +13700,9 @@
       </c>
       <c r="B861" s="1" t="inlineStr">
         <is>
-          <t>In truth, my hands didn't touch her, so my explanation
-is accurate... but the situation is only getting
-worse.</t>
+          <t>In truth, my hands didn't touch her, so my
+explanation is accurate... but the situation is only
+getting worse.</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -13771,8 +13779,8 @@
       </c>
       <c r="B866" s="1" t="inlineStr">
         <is>
-          <t>That applied to me too, and somehow I'm strangely calm
-right now.</t>
+          <t>That applied to me too, and somehow I'm strangely
+calm right now.</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -13832,7 +13840,8 @@
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
-          <t>「I didn't do anything, so Rurichiyo wouldn't get mad.」</t>
+          <t>「I didn't do anything, so Rurichiyo wouldn't get
+mad.」</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -13970,8 +13979,8 @@
       </c>
       <c r="B879" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan acts like an understanding teacher, but that
-way of putting it is way too blunt...</t>
+          <t>Nono-chan acts like an understanding teacher, but
+that way of putting it is way too blunt...</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -14077,9 +14086,9 @@
       </c>
       <c r="B886" s="1" t="inlineStr">
         <is>
-          <t>「...If someone tells you something that's hard to say,
-the adult move is not to pry any further...right,
-Nono-chan？」</t>
+          <t>「...If someone tells you something that's hard to
+say, the adult move is not to pry any
+further...right, Nono-chan？」</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -14461,8 +14470,8 @@
       <c r="B911" s="1" t="inlineStr">
         <is>
           <t>When the two of them turned toward where they'd been
-looking, a weasel had come over to the cookie Rin-chan
-had tossed earlier.</t>
+looking, a weasel had come over to the cookie
+Rin-chan had tossed earlier.</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -15034,8 +15043,8 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>Ugh, trying to get a dirty book back is even harder to
-bring up if there are two girls...</t>
+          <t>Ugh, trying to get a dirty book back is even harder
+to bring up if there are two girls...</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -15065,8 +15074,8 @@
       </c>
       <c r="B950" s="1" t="inlineStr">
         <is>
-          <t>I quietly turned the doorknob and opened the door just
-a crack.</t>
+          <t>I quietly turned the doorknob and opened the door
+just a crack.</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -15111,8 +15120,8 @@
       </c>
       <c r="B953" s="1" t="inlineStr">
         <is>
-          <t>...Just from the slight opening of the door, something
-about the room’s atmosphere felt off.</t>
+          <t>...Just from the slight opening of the door,
+something about the room’s atmosphere felt off.</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -15369,8 +15378,8 @@
       </c>
       <c r="B970" s="1" t="inlineStr">
         <is>
-          <t>They were curious, but seeing it must have embarrassed
-them.</t>
+          <t>They were curious, but seeing it must have
+embarrassed them.</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -15448,8 +15457,8 @@
       </c>
       <c r="B975" s="1" t="inlineStr">
         <is>
-          <t>It was the same shameful, unbearable feeling as when I
-showed my penis to everyone.</t>
+          <t>It was the same shameful, unbearable feeling as when
+I showed my penis to everyone.</t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -15634,8 +15643,8 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>Even when there are only girls around, she still seems
-embarrassed.</t>
+          <t>Even when there are only girls around, she still
+seems embarrassed.</t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -16249,8 +16258,8 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>「...Anyway, I think right now we have no choice but to
-examine a lot more cases.」</t>
+          <t>「...Anyway, I think right now we have no choice but
+to examine a lot more cases.」</t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -16482,8 +16491,8 @@
       </c>
       <c r="B1042" s="1" t="inlineStr">
         <is>
-          <t>Today I made dinner to suit Rurichiyo-chan's tastes as
-an apology.</t>
+          <t>Today I made dinner to suit Rurichiyo-chan's tastes
+as an apology.</t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -16513,9 +16522,9 @@
       </c>
       <c r="B1044" s="1" t="inlineStr">
         <is>
-          <t>The reason goes without saying... everyone was reading
-that thing, so I figured it’d be better to stagger the
-time.</t>
+          <t>The reason goes without saying... everyone was
+reading that thing, so I figured it’d be better to
+stagger the time.</t>
         </is>
       </c>
       <c r="C1044" t="n">
@@ -16789,8 +16798,8 @@
       </c>
       <c r="B1062" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan gives a forced smile. Rin-chan heads for the
-living room without meeting my eyes.</t>
+          <t>Miru-chan gives a forced smile. Rin-chan heads for
+the living room without meeting my eyes.</t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -16865,8 +16874,8 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan bustles about happily. Nono-chan offers
-a polite line, but her smile is strained.</t>
+          <t>Rurichiyo-chan bustles about happily. Nono-chan
+offers a polite line, but her smile is strained.</t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -17114,8 +17123,8 @@
       </c>
       <c r="B1083" s="1" t="inlineStr">
         <is>
-          <t>Really, I'm looking forward to reading it after such a
-long time.</t>
+          <t>Really, I'm looking forward to reading it after such
+a long time.</t>
         </is>
       </c>
       <c r="C1083" t="n">
@@ -17404,8 +17413,8 @@
       </c>
       <c r="B1102" s="1" t="inlineStr">
         <is>
-          <t>Taking advantage of the situation, I looked around the
-room.</t>
+          <t>Taking advantage of the situation, I looked around
+the room.</t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -17496,8 +17505,8 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>…But, do people really read erotic books together over
-and over？</t>
+          <t>…But, do people really read erotic books together
+over and over？</t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -17604,8 +17613,8 @@
       </c>
       <c r="B1115" s="1" t="inlineStr">
         <is>
-          <t>If it got passed around and read, you never know whose
-hands it might end up in.</t>
+          <t>If it got passed around and read, you never know
+whose hands it might end up in.</t>
         </is>
       </c>
       <c r="C1115" t="n">

--- a/processed_ruby_restored_xlsx/sc031_３日目.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc031_３日目.ss.xlsx
@@ -531,9 +531,9 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>It was a day off so there were no classes, but you
-could tell she was trying to take charge like a
-teacher.</t>
+          <t>It was a day off, so there were no classes, but it
+was clear Nono-chan was trying to take the lead like
+a teacher.</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -548,7 +548,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Hmm, what an adorably enthusiastic way to be…</t>
+          <t>Hmm, that's such an adorably eager way to be…</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>「It’s a treasure hunt！ When do we go？ Right now？」</t>
+          <t>"It's a treasure hunt! When shall we go? Right now?"</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -624,7 +624,8 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>「Rin wants to watch the Sunday morning shows first…」</t>
+          <t>「Rin, it'd be better to watch the Sunday-morning
+shows first…」</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -639,8 +640,8 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Weekend mornings are usually full of little-kid
-cartoons, and watching them is Rin-chan’s pleasure.</t>
+          <t>On mornings off, there are usually cartoons aimed at
+little kids, and Rin-chan enjoys watching them.</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -655,9 +656,9 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Even though she was the one who unearthed the
-Sugoroku and must be quietly excited, it’s so like
-Rin-chan that she doesn’t forget her own enjoyment.</t>
+          <t>She was the one who dug up the Sugoroku and was
+probably quietly excited, but it’s so like Rin-chan
+that she doesn't forget to enjoy herself.</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -687,7 +688,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>「I’m fine with whatever time, really.」</t>
+          <t>Any time is fine with me.</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -702,8 +703,8 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Saying that, Rurichiyo-chan spread out the sewing
-supplies that had become her holiday routine.</t>
+          <t>Even so, Rurichiyo-chan laid out the craft tools that
+had become her usual day-off routine.</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -795,7 +796,7 @@
       <c r="B22" s="1" t="inlineStr">
         <is>
           <t>When I said that gently, Nono-chan crossed her arms
-and nodded as if it made perfect sense.</t>
+as if that made perfect sense.</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -825,8 +826,8 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>「Is that so…………then shall we wait until Rin-chan
-finishes watching her show？」</t>
+          <t>I see... then shall we wait until Rin-chan finishes
+watching the anime?</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -886,7 +887,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>「………phew…！」</t>
+          <t>Phew...!</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -901,8 +902,8 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>With my nod satisfying her pride as a teacher,
-Nono-chan let out a smug, contented breath.</t>
+          <t>My nod seemed to satisfy her pride as a teacher, and
+Nono-chan let out a smug, satisfied sigh.</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -932,7 +933,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>「…So, what show are you going to watch？」</t>
+          <t>「…So, what anime are you going to watch?」</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -947,9 +948,8 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Right after putting on her teacher act, she
-immediately reverted to the same wide-eyed look as
-the others.</t>
+          <t>Right after putting on a teacherly act, she reverted
+to the same childlike expression as everyone else.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Then Nono-chan, let's watch together too！」</t>
+          <t>"Ah! Then let's watch together too, Nono-chan!"</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1024,8 +1024,8 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, remembering there was anime on, takes
-Nono-chan over in front of the TV.</t>
+          <t>Miru-chan, remembering that an anime was playing, led
+Nono-chan to the TV.</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1101,8 +1101,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>「Hah, hooooh...！  As expected of Japanimation！
-Japanese culture really is amazing...！」</t>
+          <t>"Oh—whoa...! As expected of Japanimation! Japanese
+culture really is amazing...!"</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>「What was the name of that program just now？」</t>
+          <t>「What was the name of the show we just watched?」</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>「Princess Pure Girl！ Right」</t>
+          <t>It's 'Princess Pure Girl!'</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1193,9 +1193,9 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>When Nono-chan said that, Miru-chan answered on
-reflex, and Rin-chan, who had been watching them, let
-out a small laugh.</t>
+          <t>In response to Nono-chan's words, Miru-chan
+reflexively answered, and Rin-chan, who had been
+watching, let out a soft laugh.</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1225,9 +1225,9 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>「Pripure is the third series of 'Pure Girl'... By the
-way, Rin has watched every series from the very first
-'Futari wa Pure Girl'...！」</t>
+          <t>'Pripure' is the third installment in the 'Pure Girl'
+series... By the way, Rin's watched every series
+since the very first, 'Futari wa Pure Girl'!</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1242,8 +1242,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan said, narrowing her sleepy eyes and sounding
-proud.</t>
+          <t>Rin-chan narrowed her sleepy eyes and said proudly.</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1258,8 +1257,8 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>But I wonder, does just watching them count as a
-status symbol？</t>
+          <t>But I wonder, does simply watching it count as a
+status symbol?</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1289,7 +1288,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>「Wooooow...！？ Th-that's amazing...！」</t>
+          <t>"Wooooow...!? Th-that's amazing...!"</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1319,9 +1318,9 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>She seemed to have liked it from the first time she
-saw it and was probably jealous that Rin-chan had
-watched all the previous series... I guess.</t>
+          <t>Nono-chan seemed to like it from the first time she
+saw it—maybe she’s just jealous of Rin-chan, who’s
+watched all the previous series?</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1351,8 +1350,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>「If you're doing it now, Onii-chan is recording it,
-right？」</t>
+          <t>「If it's on now, Onii-chan is recording it, right?」</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1382,7 +1380,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. For now, it's recorded, okay？」</t>
+          <t>Yeah. I've already recorded it.</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1412,8 +1410,8 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>「W-well, as expected of Janitor-sensei... I'll give
-you a gold star...！」</t>
+          <t>A-as expected of Janitor-sensei... I'll give you a
+gold star...!</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1428,7 +1426,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan glances at me from time to time.</t>
+          <t>Nono-chan keeps glancing at me.</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1503,8 +1501,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>「I think you should ask Niini. I'm pretty sure she
-has all the discs...」</t>
+          <t>「I think you should ask Onii-chan. I'm pretty sure
+they have all the discs...」</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1534,7 +1532,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Janitor-sensei is really amazing！」</t>
+          <t>Wow! Janitor-sensei is really amazing!</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1640,7 +1638,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>「...Ha！」</t>
+          <t>「...Gasp!」</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1671,8 +1669,8 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>It's like she's brushing away distracting thoughts to
-shake off temptation.</t>
+          <t>She seems to be brushing aside distracting thoughts
+to shake off temptation.</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1733,8 +1731,8 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>「…Hey！ C’mon, c’mon！ Let’s go on an adventure！
-Everyone, you’re ready, right！？」</t>
+          <t>「All right, all right! Let's go exploring! Everyone,
+are you ready!?」</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1765,7 +1763,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>...Really, what an easy-to-read kid she is...</t>
+          <t>...She's really easy to read...</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1781,7 +1779,7 @@
       <c r="B86" s="1" t="inlineStr">
         <is>
           <t>The X on the map is in the mountains on the way to
-the Gakuen.</t>
+the Academy.</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1796,9 +1794,9 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>It's a small island, but walking that far in the
-girls' shoes would be tough, so we decided to take
-the bus as close as possible.</t>
+          <t>It's a small island, but it would be too tiring for
+the girls to walk that far, so we decided to take the
+bus as close as we could.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1828,7 +1826,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>「Okay, everyone on board.」</t>
+          <t>「Okay, everyone, get on!」</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1858,7 +1856,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ Alright everyone, let's go！」</t>
+          <t>All right! Everyone, let's go!</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1873,9 +1871,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan gets in at the front and boards the bus,
-followed by Miru-chan, Rin-chan, and Rurichiyo-chan
-in that order.</t>
+          <t>Nono-chan boarded the bus first, followed by
+Miru-chan, Rin-chan, and Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1905,7 +1902,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>「…Tei！」</t>
+          <t>「...Here we go!」</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1950,7 +1947,7 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>A sudden scream rose...</t>
+          <t>Suddenly, a scream rang out...</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1965,8 +1962,9 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>Seizing a chance while Miru-chan was distracted,
-Rin-chan whimsically did her panty fortune-telling.</t>
+          <t>Seeing a chance while Miru-chan was distracted,
+Rin-chan whimsically tried a 'panties
+fortune-telling'.</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1981,8 +1979,8 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>I hurriedly turned my gaze, but I was a moment too
-late...。</t>
+          <t>I frantically turned to look, but I was a moment too
+late...</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2028,8 +2026,8 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>「Today's panties are rabbits. Today, everyone will
-have something good happen...」</t>
+          <t>"Today's panties are bunny-patterned. Today, everyone
+will probably have something good happen..."</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2074,8 +2072,8 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Because I was hoping to see her skirt flip up, our
-eyes met dead-on.</t>
+          <t>I had been staring, hoping her skirt would flip up,
+so I ended up locking eyes with Rin-chan.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2151,8 +2149,8 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan smirked for a moment, but Miru, angry,
-dragged her and they got on the bus.</t>
+          <t>Rin-chan smirked for a moment, but an angry Miru-chan
+tugged her along and they boarded the bus.</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2167,7 +2165,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>Phew, I managed to avoid being grilled about it...。</t>
+          <t>Phew... I managed to avoid being grilled about it.</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2197,8 +2195,8 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>「...Oji-sama, if you think naughty thoughts while
-driving, that's a no-no, you know？」</t>
+          <t>「...Oji-sama, if you have lewd thoughts while you're
+driving, that's unacceptable, you know?」</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2213,8 +2211,8 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Relieved, Rurichiyo-chan left that one line and
-climbed aboard the bus.</t>
+          <t>Feeling relieved, Rurichiyo-chan said a single word
+and boarded the bus.</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2229,8 +2227,8 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>...At that moment, was it obvious to Rurichiyo-chan
-that I wanted to see panties too? It must have been.</t>
+          <t>...In that moment, did even Rurichiyo-chan notice
+that I wanted to see panties?</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2245,7 +2243,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>Ugh... I should rein myself in a bit...。</t>
+          <t>Ugh... I should rein myself in a bit...</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2275,7 +2273,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>「...Hmm, there's only one spot we can stop.」</t>
+          <t>「...Hmm, this is the only place.」</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2290,8 +2288,8 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>I parked the bus in a place where the road was wide
-and it felt like a natural makeshift evacuation spot.</t>
+          <t>I parked the bus in a wide section of road that
+looked like a natural evacuation waiting area.</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2306,8 +2304,8 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>As far as I remember we could've gone a bit closer,
-but this place should be safe enough.</t>
+          <t>If I remember correctly, I could've gone a bit
+closer, but this place should be safe enough.</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2383,7 +2381,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>「Ah... yes！ Um... where exactly are we right now？」</t>
+          <t>"Ah... y-yes! Um... how far have we come now?"</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2460,7 +2458,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>「I think Rin is here…」</t>
+          <t>"I think Rin-chan is here…"</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2475,8 +2473,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan and Rin-chan each point to the place they
-think it is.</t>
+          <t>Miru-chan and Rin-chan each point to the spot they
+think they're at.</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2491,7 +2489,7 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>However, unfortunately, neither of them is right.</t>
+          <t>But unfortunately, both of them are wrong.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2552,8 +2550,8 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan points to a place where the road gets
-wider.</t>
+          <t>Rurichiyo-chan points to a spot where the road
+widens.</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2613,7 +2611,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>「Uh… well… it's just a feeling…」</t>
+          <t>「Mmm... um... it's just a hunch, really...」</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2628,8 +2626,9 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>I was right, so I asked, but Rurichiyo-chan gave an
-embarrassed smile and dodged the question.</t>
+          <t>She seemed to be right, so I asked, but
+Rurichiyo-chan gave a wry smile and dodged the
+question.</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2644,8 +2643,8 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>As the saying goes, my blind hunch hit the mark... I
-guess.</t>
+          <t>Just as the phrase says, my hunch hit the mark... I
+suppose.</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2675,7 +2674,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>「So, where is this place？」</t>
+          <t>"So, where are we?"</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2690,8 +2689,8 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan turned back to me, who was silently
-watching, and asked.</t>
+          <t>Miru-chan turned to me, who had been quietly watching
+her, and asked.</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2751,7 +2750,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>「Niini doesn't know either...？」</t>
+          <t>"Even Niini doesn't know...?"</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2766,8 +2765,8 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>When I tried to dodge it, Rin-chan gave me a look of
-pity...</t>
+          <t>When I tried to dodge the question, Rin-chan gave me
+a pitying look...</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2797,7 +2796,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>「Um... Janitor-sensei, how fast was this bus going？」</t>
+          <t>Um... Janitor-sensei, how fast was this bus going？</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2827,7 +2826,8 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ Oh... I was driving at 40 kilometers per hour？」</t>
+          <t>Huh? Oh... the bus was going 40 kilometers per hour,
+you know?</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>「...！　Really？」</t>
+          <t>"...! Really?"</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2949,8 +2949,8 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>When Rin-chan repeated the question with wide eyes,
-Nono-chan let out a smug breath.</t>
+          <t>When Rin-chan widened her eyes and asked back,
+Nono-chan let out a smug sigh.</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2980,10 +2980,10 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ First, the bus's speed is 40 km/h, but that's
-too big a unit, so let's convert it to meters per
-second. Then you get how many meters it goes in one
-second, right?」</t>
+          <t>Yes! First, the bus's speed is 40 km/h, but that's
+too large a unit, so let's convert it to meters per
+second. That will tell you how many meters it travels
+in one second, right?</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3013,9 +3013,9 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>「Next we look at the map's scale... on this map it's
-200 meters. Then you can tell how many seconds it
-takes to go every 200 meters.」</t>
+          <t>「Next, look at the map's scale... On this map it's
+200 meters. From that, you can tell how many seconds
+it takes to travel each 200 meters.」</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3045,8 +3045,9 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>「After that, you just reverse-engineer the time it
-took from the dorm to here and plug it in！」</t>
+          <t>Then all you have to do is work backwards to figure
+out how long it took from the dorm to here and apply
+it!</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3061,8 +3062,8 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>Oh... so that's how she did it...—truly teacher-like,
-a theoretical approach.</t>
+          <t>Oh... so that's how she did it... Very sensei-like —
+a thoroughly logical approach.</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3077,8 +3078,9 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>What's more, starting calculations in seconds shows
-the meticulousness of a genius.</t>
+          <t>Moreover, the fact that she starts her calculations
+in seconds speaks to a genius-level attention to
+detail.</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3124,7 +3126,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>「...o...wooow...」</t>
+          <t>「...ooh...whoa...」</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3139,8 +3141,8 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan made her mouth into a '△' shape and her eyes
-twitched at the corners.</t>
+          <t>Rin-chan puckered her mouth into a '△' shape, the
+inner corners of her eyes twitching.</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3200,8 +3202,8 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>...and at that, Miru-chan nodded as if she
-understood.</t>
+          <t>...At that point, Miru-chan nodded as if it made
+perfect sense.</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3216,9 +3218,9 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Little kids have flexible thinking, so when the gears
-click into place in their heads, they can understand
-everything at once.</t>
+          <t>Sometimes, when the gears click into place in their
+heads, little kids suddenly understand everything at
+once.</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3278,7 +3280,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... I don't understand it at all...」</t>
+          <t>"Mm... I don't get it at all..."</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3293,7 +3295,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>...Yeah, that reaction was expected too！</t>
+          <t>...Yeah, I expected that reaction!</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3323,7 +3325,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>「As expected of Nono-chan-sensei...！」</t>
+          <t>「As expected of Nono-chan-sensei!」</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3385,7 +3387,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>「...so, where are we roughly now？」</t>
+          <t>「...So, where are we now, roughly?」</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3430,9 +3432,8 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan snapped her finger and pointed, and the
-spot she indicated was just a little ahead of where
-Rurichiyo-chan had pointed.</t>
+          <t>The spot Nono-chan jabbed her finger at was just a
+little ahead of where Rurichiyo-chan had pointed.</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3447,7 +3448,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>...Just as I thought, there’s a hole in this
+          <t>...Just as I thought, there's a flaw in this
 calculation.</t>
         </is>
       </c>
@@ -3478,7 +3479,7 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>「Sensei, how did you figure out the time up to this
+          <t>「Sensei, how did you calculate the time up to this
 point？」</t>
         </is>
       </c>
@@ -3554,7 +3555,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>「That was... basically just a hunch！」</t>
+          <t>That's... basically just a rough guess!</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3615,7 +3616,8 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>「But the math worked out — pretty much right！」</t>
+          <t>「But according to the calculations, it's roughly
+correct!」</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3645,7 +3647,7 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>「See？ I knew it, right!？」</t>
+          <t>「Is that so!? I knew it, didn't I!?」</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3660,7 +3662,8 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan makes a small fist-pump with both hands.</t>
+          <t>Nono-chan clenched both fists and struck a small
+victory pose.</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3826,8 +3829,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>「Ah... no, I just happened to get it right by
-chance.」</t>
+          <t>「Ah... no, I just happened to guess correctly.」</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3843,7 +3845,7 @@
       <c r="B220" s="1" t="inlineStr">
         <is>
           <t>When Rin-chan and Miru-chan cheered, Rurichiyo-chan
-shrank down modestly.</t>
+modestly shrank back.</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3873,7 +3875,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>「Guh, gnunu...!」</t>
+          <t>「Guh... grr...!」</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3888,7 +3890,8 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan made a throaty sound, a little annoyed.</t>
+          <t>Nono-chan let out a small, frustrated throat-clearing
+sound.</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3918,9 +3921,9 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... If we'd known how long it would take up to
-this point, it would've matched sensei's
-calculations, though, right？」</t>
+          <t>Ahaha... If we'd known how long it would take to get
+here, it would have matched Sensei's calculations,
+wouldn't it?</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3950,8 +3953,8 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>「Heh... I had no idea about Miru at all, so of course
-it's sensei！」</t>
+          <t>「Heh... I never would've guessed it was Miru, so it's
+gotta be sensei!」</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3967,8 +3970,7 @@
       <c r="B228" s="1" t="inlineStr">
         <is>
           <t>Just as I was about to open my mouth to soothe
-Nono-chan, Miru-chan continued with an unabashed
-comment.</t>
+Nono-chan, Miru-chan spoke up without reservation.</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3998,7 +4000,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>「Rin still doesn't get it...」</t>
+          <t>「I still don't get it...」</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4075,8 +4077,8 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>「W-well, this time there were some uncertain
-factors... but next time will be fine！」</t>
+          <t>W-well, there were some uncertainties this time...
+but it'll be fine next time!</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4122,8 +4124,8 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>「I totally know how to read the map！ We'll go
-straight to the X without getting lost！」</t>
+          <t>I know how to read maps perfectly! We'll head
+straight to the X mark without getting lost!</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4184,7 +4186,7 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>But will it really be okay...？</t>
+          <t>But will it really be all right...?</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4199,7 +4201,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4214,7 +4216,7 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>「Everyone, make sure not to get separated, okay！」</t>
+          <t>Everyone, please don't get separated!</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4229,8 +4231,8 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>After getting off the bus, Nono-chan took the lead
-and pushed into the forest.</t>
+          <t>When we got off the bus, Nono-chan took the lead and
+led us into the forest.</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4245,8 +4247,8 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan seems to know how to read the map, but
-she's heading down a pathless route.</t>
+          <t>Nono-chan seems to know how to read maps, but the
+route ahead has no path.</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4261,8 +4263,8 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>I carried the backpack with everyone's gear and
-followed behind them.</t>
+          <t>I shouldered the backpack that held everyone's
+belongings and walked after the others.</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4307,8 +4309,8 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan checked the compass against the map and
-started walking.</t>
+          <t>Nono-chan compared the compass to the map as she
+walked.</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4323,9 +4325,8 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>Walking while dodging trees makes it easy to lose
-your sense of direction, but at this rate it seems
-fine.</t>
+          <t>Dodging trees as I walk might throw off my sense of
+direction, but at this rate I should be fine.</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4340,7 +4341,7 @@
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4370,7 +4371,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>...Then, Nono-chan's feet stopped.</t>
+          <t>…Then Nono-chan stopped in her tracks.</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4385,7 +4386,7 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>They turned to face me.</t>
+          <t>Then Nono-chan turned to face me.</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4415,7 +4416,7 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>「...Is this... okay here...？」</t>
+          <t>「...Is this okay here...?」</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4460,8 +4461,8 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>I was taken aback when she suddenly spoke so
-uncertainly.</t>
+          <t>I was taken aback when Nono-chan suddenly sounded so
+unsure.</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4491,7 +4492,8 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>「Didn't Nono-chan keep an eye on the direction？」</t>
+          <t>Wasn't Nono-chan properly keeping an eye on our
+direction?</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4521,8 +4523,8 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>「I-I was watching, but... there's trees that way and
-trees this way, so I'm a little... not confident...」</t>
+          <t>"I-I was looking, but... there are trees that way and
+trees this way, so I'm a little... unsure..."</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4568,9 +4570,9 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>I kind of knew by rough instinct, but since I thought
-this was a place where everyone should work together,
-I deliberately dodged the answer.</t>
+          <t>I thought I had a rough idea, but since this was a
+place for everyone to work together, I deliberately
+dodged the question.</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4600,7 +4602,7 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>「Eh...？ Could it be you guys are lost？」</t>
+          <t>Huh...? Could you possibly be lost?</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4630,7 +4632,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>「Ehh！？ Then does that mean we can't go home...？」</t>
+          <t>"Eh!? So does that mean we can't go home...?"</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4645,7 +4647,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>But Nono-chan's fear spread all at once.</t>
+          <t>However, Nono-chan's fear quickly spread.</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4691,7 +4693,7 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>「It's okay... if we trust Nono-chan！」</t>
+          <t>We'll be fine... as long as we trust Nono-chan!</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4721,7 +4723,7 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes！ I-I'm fine！」</t>
+          <t>「Ha... Y-yes! I-I'm fine!」</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4736,8 +4738,8 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>When encouraged cheerfully, Nono-chan clenched both
-hands.</t>
+          <t>When I cheered her on cheerfully, Nono-chan clenched
+her fists.</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4767,7 +4769,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>「Really？ Are you really okay！？」</t>
+          <t>「Really? Are you really okay?!」</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4797,7 +4799,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">「Th-this way！ </t>
+          <t xml:space="preserve">T-this way... </t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4812,7 +4814,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Surely</t>
+          <t>I'm sure!</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4827,7 +4829,7 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>...maybe</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4842,7 +4844,7 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>...」</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4857,7 +4859,8 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>...Nono-chan tried to bluff in English.</t>
+          <t>...Nono-chan was trying to dodge it by using English,
+huh.</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4933,7 +4936,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>「...This way.」</t>
+          <t>「...Over here.」</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4948,7 +4951,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>And then she trots along.</t>
+          <t>Then she trotted off.</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5008,7 +5011,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>「W-What's… wrong？」</t>
+          <t>「W-What's... wrong?」</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5145,7 +5148,7 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>「This place…！」</t>
+          <t>「This is…！」</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5175,7 +5178,7 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>「Wow…！ This is wonderful…！」</t>
+          <t>Oh my...! How lovely...!</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5206,9 +5209,8 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>The place where Rin-chan had stopped was bright,
-sunlight pouring down through the trees, a well-lit
-spot even in the forest.</t>
+          <t>The spot where Rin-chan stopped was bathed in dappled
+sunlight, bright even within the forest.</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5238,8 +5240,8 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Look over there, in front of that rock…！ There's
-some kind of can buried！」</t>
+          <t>「Ah! Look— in front of that rock...! There's some
+kind of can buried there!」</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5254,8 +5256,8 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>Then Miru-chan, who had keenly spotted something, let
-out an excited voice.</t>
+          <t>Then Miru-chan, having spotted something, gave an
+excited shout.</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5270,8 +5272,8 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>Looking closer, a round cookie tin was half exposed,
-buried in the ground.</t>
+          <t>On closer inspection, a round cookie tin was
+half-buried in the ground.</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5331,7 +5333,7 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>「Yay！ Then that must be the treasure…！」</t>
+          <t>"Yay! So that's the treasure...!"</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5376,8 +5378,8 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>Thinking we'd reached the X mark, everyone's spirits
-went up.</t>
+          <t>Thinking they'd reached the spot marked with an X,
+everyone's excitement rose.</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5422,9 +5424,9 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>...Meanwhile, Rin-chan strolled along at her own pace
-with a little patter and yanked out a can that was
-half-buried in the ground.</t>
+          <t>Meanwhile, Rin-chan walked along at her own pace, her
+little footsteps pattering, and yanked out a can that
+was half-buried in the ground.</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5454,7 +5456,7 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>「...Too bad, this was Ruri's cookie tin.」</t>
+          <t>「...Too bad, this was Rin-chan's cookie tin.」</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5469,8 +5471,8 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>When Rin-chan popped open the cookie tin, there were
-definitely dagashi inside.</t>
+          <t>Sure enough, when Rin-chan popped open the cookie
+tin, it contained dagashi.</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5500,7 +5502,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>「Ehhh～～～～...」</t>
+          <t>「Eeeeeee...」</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5515,8 +5517,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>...Taken aback by the unexpected discovery, everyone
-froze in surprise...</t>
+          <t>…Startled by the unexpected turn, everyone froze…</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5531,7 +5532,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>I was surprised too, but there was a bigger problem.</t>
+          <t>I was surprised too, but there was an even bigger
+problem.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5561,8 +5563,8 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>「W-wait, Rin-chan！ Why is Rin-chan's candy tin in a
-place like this！？」</t>
+          <t>「W-wait, Rin-chan! Why are Rin-chan's snacks in a
+place like this!?」</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5592,7 +5594,7 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>「...That's because I hid it here.」</t>
+          <t>...That's because Rin-chan hid it.</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5622,7 +5624,8 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>「So you knew you'd be coming here from the start？」</t>
+          <t>"So, Rin-chan, did you know from the start that you'd
+be coming here?"</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5652,8 +5655,8 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t>「No, I hadn't entered from there, but I realized it
-partway through.」</t>
+          <t>No, I hadn't come in through there before, but I
+realized it partway through.</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -5683,8 +5686,8 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>「No, no, that's not it—why did you come all the way
-here！？」</t>
+          <t>「No, no, that's not it — why did you come all the way
+out here!?」</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5714,7 +5717,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>「Fufufufu...」</t>
+          <t>「Hehehe...」</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5729,8 +5732,8 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan laughed meaningfully, pinched a piece of
-dagashi, and took it out.</t>
+          <t>Rin-chan gave a knowing smile, pinched out a piece of
+dagashi.</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5760,7 +5763,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>「T-then... this wasn't the place after all...？」</t>
+          <t>"W-well then... wasn't it here...?"</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5775,8 +5778,8 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>Before I could press Rin-chan, Nono-chan let out a
-tragic little voice.</t>
+          <t>Before I could press Rin-chan for an answer,
+Nono-chan let out a pitiful cry.</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5913,8 +5916,8 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>「Well... besides, I was the one who made that
-sugoroku in the first place.」</t>
+          <t>"Well... besides, I was the one who made that
+Sugoroku in the first place."</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5929,7 +5932,7 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>By this point, I finally remembered.</t>
+          <t>Once I got this far, I finally remembered.</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5944,7 +5947,7 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t>I buried something in this spot.</t>
+          <t>I had buried something here.</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -6004,7 +6007,7 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>「Ooh~！」</t>
+          <t>「Ooh...!」</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6019,8 +6022,8 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>Striking a confident pose, Nono-chan's eyes shone
-bright.</t>
+          <t>Nono-chan struck a confident pose and her eyes lit
+up.</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6035,7 +6038,7 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>...Thanks for the honest reaction.</t>
+          <t>…Thanks for being so honest.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6065,7 +6068,7 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan！ Shovel！ Get the shovel out！」</t>
+          <t>「Onii-chan! Shovel! Bring the shovel!」</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -6080,7 +6083,7 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>Eager Miru-chan grabs my backpack and tries to pull
+          <t>Impatient Miruku grabs my backpack and tries to pull
 it down.</t>
         </is>
       </c>
@@ -6141,7 +6144,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>「Niini, you're slow...！」</t>
+          <t>「Niini, you're late...!」</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6156,8 +6159,8 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, who'd been relaxed until just now, starts
-hounding me along with Miru-chan.</t>
+          <t>Rin-chan, who'd been the only one relaxed until just
+now, joins Miru-chan in pestering me.</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6187,7 +6190,7 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama, please hurry up！」</t>
+          <t>「Oji-sama, please hurry!」</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -6202,7 +6205,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>Even Rurichiyo-chan unusually rushes me.</t>
+          <t>Even Rurichiyo-chan is unusually urging me on.</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6218,7 +6221,7 @@
       <c r="B375" s="1" t="inlineStr">
         <is>
           <t>Everyone seems fixated on the X mark on the Sugoroku
-board, but what exactly did I bury...？</t>
+board, but what exactly did I bury...?</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -6264,7 +6267,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ I found it, I found it！」</t>
+          <t>“Ah! There it is! There it is!”</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6279,8 +6282,8 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t>...About ten minutes of digging the ground with a
-shovel.</t>
+          <t>...It took about ten minutes to dig up the ground
+with a shovel.</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -6295,8 +6298,8 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>Just beneath the can Rin-chan had half-buried, we
-unearthed a square senbei tin.</t>
+          <t>We dug up a square tin of senbei just beneath the can
+Rin-chan had half-buried.</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6326,7 +6329,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ This is it, right！？」</t>
+          <t>「I found it! This is it, right!?」</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6341,8 +6344,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, who found it first, squeals with
-excitement.</t>
+          <t>Miru-chan, who found it first, is ecstatic.</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6372,7 +6374,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>「I wonder what could be inside...？」</t>
+          <t>「I wonder what's inside...?」</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6402,8 +6404,8 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>「I have a feeling there's treasure here that Rin
-wants...！」</t>
+          <t>「I feel like there's another treasure Rin's looking
+for...!」</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6433,8 +6435,8 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu... So, that means it might have old sweets
-inside, right？」</t>
+          <t>“Hehe... So you mean there might be some old sweets
+inside?”</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6464,7 +6466,7 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>And then, her expression softened and warmed.</t>
+          <t>Then her expression softened into a warm one.</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6494,8 +6496,9 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>「...But it was something Oji-sama buried when I was
-little... I'm curious what's inside.」</t>
+          <t>「...But is it something Oji-sama buried when he was
+little...? I'm looking forward to seeing what's
+inside.」</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -6525,8 +6528,8 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>「That's right... and since I even went so far as to
-leave a riddle on a Sugoroku...！」</t>
+          <t>That's right... after all, he even went so far as to
+leave a riddle on the Sugoroku...!</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -6556,7 +6559,7 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>「...So, there really is treasure inside！？」</t>
+          <t>“So... there's really treasure inside!?”</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -6586,7 +6589,7 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t>「Rare stuff... rare stuff...！」</t>
+          <t>「Rare things... rare things...!」</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -6601,7 +6604,7 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>Hmm, everyone's expectations are rising.</t>
+          <t>Hmm, everyone's getting their hopes up.</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6616,8 +6619,8 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>That said, since I was the one who buried it, I don't
-really think I can live up to everyone's hopes...</t>
+          <t>That said, since it's something I buried, I don't
+think it will live up to everyone's expectations...</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6647,7 +6650,7 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>「...Shall we open it then？」</t>
+          <t>「...Well then, shall we open it?」</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6707,7 +6710,7 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>「Rare stuff... come to me」</t>
+          <t>「Rare things... come!」</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -6737,8 +6740,8 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>「The one who found it first, Miruku-chan, please open
-it.」</t>
+          <t>Miruku-chan, please open it — you were the first to
+find it.</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -6753,8 +6756,7 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>I watched over them as they excitedly tried to open
-it.</t>
+          <t>I watched as everyone eagerly tried to open it.</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -6801,7 +6803,7 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t>「Okay... I'll open it...？」</t>
+          <t>「All right... I'll open it, okay...?」</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -6816,8 +6818,8 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>And Miru-chan, with unusually cautious hands, opened
-the tin's lid...</t>
+          <t>Miru-chan opened the lid of the tin with a more
+cautious touch than usual...</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6862,8 +6864,8 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>At a glance, an electric shock ran through my whole
-body and all my memories came back.</t>
+          <t>The moment I saw it, an electric shock ran through my
+whole body and all my memories came flooding back.</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6923,7 +6925,7 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t>「Oh, looks like... a book？」</t>
+          <t>「Oh—it's... a book, isn't it?」</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6983,7 +6985,7 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>「...No, it's not.」</t>
+          <t>「...No, that's not it.」</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -7013,7 +7015,8 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>After all, the cover has a picture of a cute girl.</t>
+          <t>After all, the cover bore an illustration of a cute
+girl.</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7028,7 +7031,7 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t>...and its very name is Comic RO！</t>
+          <t>…It's called Comic RO!</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -7043,8 +7046,8 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>To put it simply, it’s an erotic manga magazine made
-up entirely of very tiny kids.</t>
+          <t>To put it simply, it’s an erotic manga magazine that
+features nothing but very young children.</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7090,8 +7093,8 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>…Hmm, I can’t even count how many times this book has
-helped me….</t>
+          <t>…Hmm, I can't even begin to count how many times I've
+relied on this book...</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7106,8 +7109,8 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>I miss it... for me, who spent my adolescence on this
-island, this was literally my bible.</t>
+          <t>How nostalgic... For me, who spent my adolescence on
+this island, this was truly my bible.</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -7122,8 +7125,8 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t>As long as you live on this island, when you’re a
-kid, even if you want one you can’t get it.</t>
+          <t>As long as I lived on this island, I couldn't get one
+as a child, even if I wanted to.</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -7188,7 +7191,7 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>And now to be able to see it again like this...！</t>
+          <t>I can't believe I can see it again like this...！</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7203,7 +7206,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>................But it's not in great shape, is it.</t>
+          <t>...But it's not in very good condition.</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7233,7 +7236,8 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>「What kind of book is it... shall I take a look？」</t>
+          <t>I wonder what kind of book this is... Shall I take a
+look?</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7294,8 +7298,8 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>When I hurriedly stopped her, Miru-chan's face
-immediately looked visibly annoyed.</t>
+          <t>When I hurriedly stopped her, Miru-chan immediately
+looked annoyed.</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7325,7 +7329,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t>「Why not？ Just a little bit is fine, right？」</t>
+          <t>Why? Can't I just take a quick peek?</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7385,8 +7389,8 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t>「It's a book I used to treasure, so it has memories
-for me！」</t>
+          <t>"It's a book I treasured when I was younger, so it
+means a lot to me!"</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -7401,8 +7405,8 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan went along with Miru-chan, but I shot back
-with a more plausible-sounding line.</t>
+          <t>Rin-chan sided with Miru-chan, but I retorted with a
+more plausible-sounding remark.</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -7432,7 +7436,7 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t>「Indeed, it's just as Janitor-sensei said.」</t>
+          <t>Indeed, it's just as Janitor-sensei said.</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -7447,7 +7451,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>As expected, Nono-chan understands what's reasonable.</t>
+          <t>As expected, Nono-chan knows what's what.</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7493,8 +7497,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t>...As expected, Nono-chan understands what's
-reasonable...</t>
+          <t>...As expected, Nono-chan knows what's what...</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -7524,7 +7527,7 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t>「B-but you know...」</t>
+          <t>「B-but...」</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -7554,8 +7557,8 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>The only one left who might understand how I feel is
-Rurichiyo-chan！</t>
+          <t>The only person who would understand how I feel now
+is Rurichiyo-chan!</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7615,7 +7618,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>W-weak by majority vote...？</t>
+          <t>T-that's an overwhelming loss by majority vote...?</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7691,7 +7694,7 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
-          <t>「………………huh？」</t>
+          <t>「………………Huh?」</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -7721,7 +7724,7 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t>「...！！」</t>
+          <t>「…!!」</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -7766,8 +7769,9 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t>The wonder of manga... is that just from the pictures
-you can understand the story, the situation.</t>
+          <t>The wonderful thing about manga... is that you can
+understand the story and the situation just by
+looking at the pictures.</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -7797,8 +7801,8 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>「Th-there are kids about the same age as all of you
-doing, um, naughty things...」</t>
+          <t>"Th-there are girls about the same age as you all
+doing... um, naughty things..."</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -7937,7 +7941,7 @@
       <c r="B487" s="1" t="inlineStr">
         <is>
           <t>「M-m-m, I think it's still a little too early for you
-all！ This is a bosshuu！」</t>
+all! This is indecent!」</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -7952,8 +7956,7 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan shouted, pouting with a bright red face in
-anger.</t>
+          <t>Nono-chan shouted in a huff, her face bright red.</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -8014,8 +8017,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>「Y-You too, Janitor-sensei！ I think lewd stuff is
-wrong！」</t>
+          <t>Y-You too, Janitor-sensei! I don't think lewd things
+are okay!</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8030,8 +8033,8 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>Ahh... the atmosphere says no matter what I say, they
-won't listen...</t>
+          <t>Ah... it feels like they won't listen to anything I
+say...</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8091,8 +8094,8 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>「All right！ Then be sure to come pick it up later,
-Janitor-sensei！」</t>
+          <t>All right! Then, Janitor-sensei, be sure to come pick
+it up later!</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8107,8 +8110,7 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>When I apologized obediently, Nono-chan nodded with a
-triumphant look.</t>
+          <t>When I apologized meekly, Nono-chan nodded smugly.</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -8123,7 +8125,7 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>Ahh... my Comic RO...</t>
+          <t>Ah... my Comic RO...</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8138,8 +8140,8 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t>But if they'll give it back later, I guess I'll let
-it slide？</t>
+          <t>But if she gives it back later, I guess I'll let it
+go.</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -8154,9 +8156,8 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>Still, since I couldn't face everyone either way, I
-turned away and let out a huge, huge sigh inside my
-heart...</t>
+          <t>Still, since I couldn't face everyone anyway, I
+turned away and let out a deep, deep sigh...</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8186,7 +8187,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>「Weee're heeere~」</t>
+          <t>「Here I am~」</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -8231,7 +8232,7 @@
       </c>
       <c r="B506" s="1" t="inlineStr">
         <is>
-          <t>Guided by Rin-chan, we arrived at the cove.</t>
+          <t>Guided by Rin-chan, we arrived at Irie (the Cove).</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -8246,9 +8247,9 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>Why Rin-chan led us, or whether she could even get
-into the woods in the first place, turned out to be
-simple once we understood.</t>
+          <t>Why Rin-chan had guided us—or how she had even
+managed to get into the forest in the first place—was
+easy to understand once we found out.</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -8263,8 +8264,8 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>There was actually a shortcut, so it was easy to come
-from the cove.</t>
+          <t>Actually, there was a shortcut, so we could easily
+get here from the cove.</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8279,9 +8280,9 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>Even though I was a boy, back when I was a kid I
-could come into the woods too, so it made sense that
-there'd be a path like that.</t>
+          <t>Even if he's just a kid, I could get into the woods
+when I was younger too, so it's only natural that
+there would be a path like that.</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8311,7 +8312,7 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>「Ooohhhh... whoaaa~~~！」</t>
+          <t>「Ooooh... wow~~~！」</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8356,9 +8357,9 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t>「Come to think of it, you said you wanted to come
-while the sun was still up, so your wish kind of came
-true unexpectedly, huh？」</t>
+          <t>"Come to think of it, you said you wanted to come
+while it was still daylight, so your wish
+unexpectedly came true, didn't it?"</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -8403,9 +8404,9 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t>When I lightly called out, remembering the first time
-we came here, Nono-chan answered so honestly and
-happily.</t>
+          <t>I called out softly, remembering the first time I
+came here, and Nono-chan responded very
+straightforwardly and happily.</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -8435,7 +8436,7 @@
       </c>
       <c r="B519" s="1" t="inlineStr">
         <is>
-          <t>「Well… isn't this nice？」</t>
+          <t>Well... that's good, isn't it?</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -8465,7 +8466,7 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ It's really beautiful！」</t>
+          <t>Yes! It's so beautiful!</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8480,8 +8481,9 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan sounded like a mother talking to her
-girls, and they replied just as honestly.</t>
+          <t>Rurichiyo-chan adopted a motherly tone as if speaking
+to a daughter, and Nono-chan responded just as
+straightforwardly.</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8496,7 +8498,7 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>Really, she’s such an innocent sort of teacher….</t>
+          <t>Really, she's such a childlike teacher...</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8526,8 +8528,7 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>「That’s right！ Since we’re here, shall we have our
-lunch here？」</t>
+          <t>Yes! Since we’re here, shall we eat our bento here?</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -8557,7 +8558,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Sounds great！ Nice idea！」</t>
+          <t>That sounds great! What a nice idea!</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8587,8 +8588,8 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha！ Eating a bento in a place like this is kind
-of romantic, right？！」</t>
+          <t>Ahaha！ Eating a bento in a place like this is kind of
+romantic, right？！</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8618,8 +8619,8 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, it feels like a sea fairy might bring us some
-sweets.」</t>
+          <t>Yeah, it feels like sea fairy-san might bring us some
+sweets.</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -8680,7 +8681,7 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>「Okay, I'll lay out the sheet.」</t>
+          <t>Okay, I'll lay out the sheet.</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8710,7 +8711,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>「Then I’ll bring out Miru’s bento~！」</t>
+          <t>Then I'll bring out Miruku's bento~!</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -8740,7 +8741,7 @@
       </c>
       <c r="B539" s="1" t="inlineStr">
         <is>
-          <t>「Then I'll bring the snacks…！」</t>
+          <t>Then I'll bring the snacks...!</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -8755,8 +8756,9 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>While I pulled a folded sheet out of my rucksack,
-everyone helped get things ready in their own way.</t>
+          <t>While I was taking a folded picnic sheet out of my
+rucksack, everyone helped with the preparations in
+their own ways.</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -8786,9 +8788,8 @@
       </c>
       <c r="B542" s="1" t="inlineStr">
         <is>
-          <t>「Ah… everyone, before touching the food, let's make
-sure to properly wipe our hands with wet wipes,
-okay？」</t>
+          <t>Ah... everyone, before touching the food, please wipe
+your hands properly with a wet wipe, okay?</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -8803,8 +8804,8 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>And Rurichiyo-chan fussed over the others on my
-behalf.</t>
+          <t>And Rurichiyo-chan took care of the other kids for
+me.</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -8834,8 +8835,8 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>「Knowing something like this might happen, I brought
-wet towels for everyone！」</t>
+          <t>I thought this might happen, so I brought wet towels
+for everyone!</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -8866,8 +8867,8 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>I watched that sight, smiling, as I spread the sheet
-out.</t>
+          <t>I watched them with a fond smile and spread out the
+sheet.</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -8882,7 +8883,7 @@
       </c>
       <c r="B548" s="1" t="inlineStr">
         <is>
-          <t>And at the same time, I thought.</t>
+          <t>And at the same time, I thought to myself.</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -8897,7 +8898,7 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>Comic RO… I wonder when I'll be able to return it？</t>
+          <t>Comic RO... I wonder when I'll get it back?</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -8912,7 +8913,7 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>After lunch it became free time.</t>
+          <t>After lunch, we had free time.</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -8927,8 +8928,7 @@
       </c>
       <c r="B551" s="1" t="inlineStr">
         <is>
-          <t>Everyone liked this spot, and there was plenty of
-time.</t>
+          <t>Everyone liked this spot, and we had plenty of time.</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="B553" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chaaaan！ Over here—！」</t>
+          <t>Rurichiyo-chan~! Over here~!</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="B555" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah！ Please wait…！」</t>
+          <t>"Ah—! Ah—! Please wait...!"</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>She ran along the water's edge, dragging
+          <t>She was running along the water's edge, swinging
 Rurichiyo-chan around.</t>
         </is>
       </c>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>「Niini, niini…！」</t>
+          <t>「Niini, Niini...!」</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>「There, there…！」</t>
+          <t>「Look, look...!」</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>「Huh？　Oh….」</t>
+          <t>「Eh? Oh...」</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -9203,8 +9203,8 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>And just behind the nearest tree, a small creature
-was peeking around, looking startled.</t>
+          <t>Peeking out from behind the nearest tree was a single
+small animal, looking bewildered.</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
-          <t>「Wow！ So cute—！」</t>
+          <t>「Wow! So cute!」</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
-          <t>「Shh！ You'll scare it away, shh…！」</t>
+          <t>Shh! It'll run away—shh...</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -9279,8 +9279,8 @@
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
-          <t>To Miru-chan, who had cried out in delight, Rin-chan
-put her index finger to her lips.</t>
+          <t>Rin-chan holds up an index finger to her lips to
+shush Miru-chan, who cried out in delight.</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>「I wonder… what is that？」</t>
+          <t>「I wonder what that is?」</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
-          <t>「Oh？ That's a weasel.」</t>
+          <t>「Oh? That's Itachi-san.」</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -9416,8 +9416,8 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>「Well, MiruMiru's hobby is collecting animal panties,
-after all...」</t>
+          <t>「Well, Miruku's hobby is collecting animal-print
+panties, after all...」</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>「W-wait, Rin...」</t>
+          <t>「W-wait, Rin-chan...」</t>
         </is>
       </c>
       <c r="C585" t="n">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="B587" s="1" t="inlineStr">
         <is>
-          <t>「MiruMiru, shh...！」</t>
+          <t>「Miruku, shh...！」</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -9492,9 +9492,8 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>Even though Rin herself had stirred things up, she
-warned Miru-chan when Miru-chan opened her mouth to
-speak.</t>
+          <t>Even though Rin-chan herself had provoked it, she
+held Miru-chan back when Miru-chan tried to speak.</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -9509,8 +9508,8 @@
       </c>
       <c r="B589" s="1" t="inlineStr">
         <is>
-          <t>Well, they're wild animals — if you make a lot of
-noise they'll run away.</t>
+          <t>Well, it's a wild animal — if you make a lot of noise
+it'll run away.</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -9540,7 +9539,7 @@
       </c>
       <c r="B591" s="1" t="inlineStr">
         <is>
-          <t>「Is that an Itachi... I've never seen one before...！」</t>
+          <t>Is that Itachi-san...? I've never seen one before...!</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -9586,8 +9585,8 @@
       </c>
       <c r="B594" s="1" t="inlineStr">
         <is>
-          <t>「As expected, this island is full of nature. It's
-really moving...！」</t>
+          <t>「No wonder this island is so full of nature. I'm so
+moved...!」</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -9617,8 +9616,8 @@
       </c>
       <c r="B596" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... but they're basically nocturnal, so seeing
-one was lucky.」</t>
+          <t>Yeah... but it's actually nocturnal, so we're lucky
+to have seen it.</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -9633,8 +9632,8 @@
       </c>
       <c r="B597" s="1" t="inlineStr">
         <is>
-          <t>While going along with Nono-chan's excitement, Rin
-tugged at my clothes to get my attention.</t>
+          <t>As I was going along with Nono-chan, Rin-chan kept
+tugging at my clothes.</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -9694,7 +9693,7 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>「Who knows？ Why don't you try giving it one？」</t>
+          <t>「I wonder... Why don't you try giving it one?」</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -9739,7 +9738,7 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>Rin pulled a cookie out of the snack bag.</t>
+          <t>Rin-chan took a cookie out of the snack bag.</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -9769,7 +9768,8 @@
       </c>
       <c r="B606" s="1" t="inlineStr">
         <is>
-          <t>「If you get closer it might run away, you know...？」</t>
+          <t>It might run away if we get closer... don't you
+think?</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>Taking Nono-chan's advice, Rin tossed the cookie
+          <t>Taking Nono-chan's advice, Rin-chan tossed the cookie
 underhand.</t>
         </is>
       </c>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>Itachi</t>
+          <t>weasel-san</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>「Ah—there it goes~」</t>
+          <t>「Ah—it's gone~」</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>「I wanted the Itachi to eat the cookie...」</t>
+          <t>"I wanted weasel-san to eat the cookie..."</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -10015,8 +10015,8 @@
       </c>
       <c r="B622" s="1" t="inlineStr">
         <is>
-          <t>「Well, if you leave it there it'll probably come back
-to eat it later.」</t>
+          <t>「Well, if you just leave it there, it'll probably
+come back later to eat it.」</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>「Yeah............」</t>
+          <t>「Yeah...」</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -10061,8 +10061,8 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>Hajime gives a tiny bit of reassurance, but Rin-chan
-still pouts.</t>
+          <t>Hajime offered a little reassurance, but Rin-chan
+still pouted.</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10077,8 +10077,9 @@
       </c>
       <c r="B626" s="1" t="inlineStr">
         <is>
-          <t>When she said she wanted it to eat it, she probably
-really meant she was frustrated it didn't get to.</t>
+          <t>When she said she wanted weasel-san to eat it, she
+probably meant it literally; she was genuinely
+disappointed that it hadn't been eaten.</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -10108,8 +10109,8 @@
       </c>
       <c r="B628" s="1" t="inlineStr">
         <is>
-          <t>「Come to think of it, Ruri-chan is afraid of Itachi,
-right?」</t>
+          <t>Come to think of it, Ruri-chan, you're not good with
+Itachi, are you?</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -10169,8 +10170,8 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. Before, we saw one near the Gakuen together
-and she yelled 'big mouse!' and ran away—」</t>
+          <t>「Yeah. Earlier, when we saw one together near the
+Academy, Ruri-chan shouted 'big mouse!' and ran off—」</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -10200,8 +10201,8 @@
       </c>
       <c r="B634" s="1" t="inlineStr">
         <is>
-          <t>「Is that so？ Well, some people just have things
-they're not good with.」</t>
+          <t>"Oh, is that so? Well, if someone's uncomfortable
+around them, that's to be expected."</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -10216,8 +10217,8 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>While Miru-chan talks, Nono-chan nods along and
-suddenly smiles slightly.</t>
+          <t>As Miru-chan spoke, Nono-chan, who was nodding along,
+suddenly broke into a brief smile.</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -10247,9 +10248,9 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>「Ah, but maybe ferrets would be okay？ Ferrets are
-pure white and cute, and I hear they become really
-attached to people when kept as pets, you know？」</t>
+          <t>Ah, but maybe ferrets would be okay? Ferrets are pure
+white and cute, and I hear they get very attached to
+people when kept as pets.</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10279,7 +10280,7 @@
       </c>
       <c r="B639" s="1" t="inlineStr">
         <is>
-          <t>「Ah, I see—so ferrets are related to Itachi.」</t>
+          <t>"Ah, I see—ferrets are members of the weasel family."</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -10309,7 +10310,7 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>「Huh, so there are ferrets that are Itachi？」</t>
+          <t>「Huh, so ferrets are a kind of Itachi?」</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10354,7 +10355,7 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>We all admired Nono-chan's little lecture together.</t>
+          <t>We were all impressed by Nono-chan's knowledge.</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -10414,9 +10415,9 @@
       </c>
       <c r="B648" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ In Japan there's a kind of Itachi called an
-okojo. In winter their fur turns pure white and
-they're so cute.」</t>
+          <t>"Ah! There's also a kind of Itachi in Japan called
+the okojo. In winter their fur turns pure white, and
+they're very cute."</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -10447,7 +10448,7 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>Still so easy to read…</t>
+          <t>As always, so easy to understand...</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -10477,7 +10478,7 @@
       </c>
       <c r="B652" s="1" t="inlineStr">
         <is>
-          <t>「Ah… by the way, where's Rurichiyo-chan？」</t>
+          <t>「Ah… by the way, where's Ruri-chan?」</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -10507,8 +10508,8 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ Now that you mention it, I don't see her
-anywhere？」</t>
+          <t>Huh? Now that you mention it, I don't see her
+anywhere.</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -10538,8 +10539,8 @@
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>「Muu？ Wasn't Rin with Nono-chan until Rin spotted the
-Itachi？」</t>
+          <t>「Hmm? Weren't you with Nono-chan until Rin found
+Itachi-san?」</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -10569,7 +10570,7 @@
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>「Maybe Rurichiyo ran off before the Itachi did？」</t>
+          <t>「Maybe Ruri-chan ran off before Itachi-san did?」</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -10584,8 +10585,8 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>Like she saw the Itachi from afar and couldn't help
-but bolt, maybe？</t>
+          <t>Maybe she saw Itachi-san from afar and couldn't help
+but run off?</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -10615,7 +10616,8 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha, would something like that happen like a gag？」</t>
+          <t>Haha, would something like that really happen, like
+in a gag?</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -10630,8 +10632,8 @@
       </c>
       <c r="B662" s="1" t="inlineStr">
         <is>
-          <t>…It's turned into a laughable little moment, but
-thinking about it properly makes me worried.</t>
+          <t>It's become a lighthearted, joking mood, but on
+second thought I get worried.</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -10692,7 +10694,7 @@
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>I searched around the cove, but couldn't find
+          <t>I searched around Irie (the Cove), but couldn't find
 Rurichiyo-chan.</t>
         </is>
       </c>
@@ -10723,8 +10725,8 @@
       </c>
       <c r="B668" s="1" t="inlineStr">
         <is>
-          <t>Like Rin said, that she was so startled by the Itachi
-that she ran away… I think that's a bit off.</t>
+          <t>As Rin-chan said, I don't think it's quite right to
+say she ran off because the weasel startled her.</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -10755,7 +10757,7 @@
       </c>
       <c r="B670" s="1" t="inlineStr">
         <is>
-          <t>Then, let's think of other reasons.</t>
+          <t>In that case, let's consider other possibilities.</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -10786,9 +10788,9 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>Then I noticed that aside from the animal trail Rin
-had shown, there was a spot that looked like it led
-into the forest.</t>
+          <t>Then I noticed that, apart from the animal trail
+Rin-chan had shown us, there was a place that looked
+like it led into the woods.</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -10803,7 +10805,7 @@
       </c>
       <c r="B673" s="1" t="inlineStr">
         <is>
-          <t>...Could she have gone into the forest？</t>
+          <t>...No way — could she have gone into the woods?</t>
         </is>
       </c>
       <c r="C673" t="n">
@@ -10849,7 +10851,8 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>...She's not in sight, so let's go check for now.</t>
+          <t>...She's nowhere to be seen, so let's go look for
+her.</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -10864,8 +10867,7 @@
       </c>
       <c r="B677" s="1" t="inlineStr">
         <is>
-          <t>I pick a spot that looks like a person could get
-through and go on.</t>
+          <t>I choose a spot that looks passable and head in.</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -10880,9 +10882,9 @@
       </c>
       <c r="B678" s="1" t="inlineStr">
         <is>
-          <t>Even if she had gone into the woods, Rurichiyo-chan
-wouldn’t have gone out of her way to walk into a
-place that’s hard to get through.</t>
+          <t>Even if she'd gone into the woods, Rurichiyo-chan
+wouldn't have deliberately gone into an area that's
+hard to get through.</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -10897,8 +10899,8 @@
       </c>
       <c r="B679" s="1" t="inlineStr">
         <is>
-          <t>As I was thinking that and walking, before long I was
-able to find Rurichiyo-chan.</t>
+          <t>As I walked, thinking that, I soon found
+Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -10974,7 +10976,7 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>「Huh...？!」</t>
+          <t>「Huh...?!」</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -11034,8 +11036,8 @@
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan sighed, pulled down her panties, and
-squatted while gripping the hem of her dress.</t>
+          <t>With a sigh, Rurichiyo-chan pulled her panties down
+and squatted, clutching the hem of her dress.</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -11066,8 +11068,8 @@
       <c r="B690" s="1" t="inlineStr">
         <is>
           <t>Realizing why Rurichiyo-chan had moved away from
-everyone, I also lost the nerve to step out from
-behind the tree.</t>
+everyone, I simultaneously missed my chance to step
+out from behind the tree.</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -11082,8 +11084,8 @@
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>She mustn't find out I'm here until she's finished
-peeing and has pulled her panties back up.</t>
+          <t>Rurichiyo-chan mustn't find out I'm here until she's
+finished peeing and has pulled her panties back up.</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -11098,7 +11100,7 @@
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
-          <t>...But, would it be so wrong to sneak a peek？</t>
+          <t>...But would it be so wrong to sneak a peek?</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -11128,8 +11130,8 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>「Hah... it's a little embarrassing to do this in a
-place like this...」</t>
+          <t>"Sigh... I'm a little embarrassed to be peeing in a
+place like this..."</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -11144,7 +11146,7 @@
       </c>
       <c r="B695" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan really talks to herself as if she’s
+          <t>Rurichiyo-chan mumbles to herself, clearly
 embarrassed.</t>
         </is>
       </c>
@@ -11191,8 +11193,8 @@
       </c>
       <c r="B698" s="1" t="inlineStr">
         <is>
-          <t>Because they were raised by the Arisugawa family,
-they feel reluctant to pee anywhere but a toilet.</t>
+          <t>Because she was raised by the Arisugawa family, she
+feels reluctant to pee anywhere but a toilet.</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -11207,7 +11209,7 @@
       </c>
       <c r="B699" s="1" t="inlineStr">
         <is>
-          <t>Especially outdoors...！</t>
+          <t>Doing it outdoors...!</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -11237,8 +11239,9 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>「I snuck away from everyone's sight, but if I don't
-hurry they'll notice I'm gone...」</t>
+          <t>「I went to the trouble of sneaking away from
+everyone's view, but if I don't hurry, they'll
+realize I'm not here...」</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -11254,7 +11257,7 @@
       <c r="B702" s="1" t="inlineStr">
         <is>
           <t>Even though no one's watching, Rurichiyo-chan is
-still worried about people's eyes.</t>
+still worried about being seen by others.</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -11299,8 +11302,8 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>「Since it's my oji-sama, if I notice I'll come
-looking for me, phew...」</t>
+          <t>"It's Oji-sama, so if he notices, he'll probably come
+looking for me... phew..."</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11315,7 +11318,8 @@
       </c>
       <c r="B706" s="1" t="inlineStr">
         <is>
-          <t>...As expected, Rurichiyo-chan understands this well.</t>
+          <t>As expected, Rurichiyo-chan knows exactly what's
+going on.</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -11330,8 +11334,8 @@
       </c>
       <c r="B707" s="1" t="inlineStr">
         <is>
-          <t>What would my reaction be if I walked out and said
-I'm actually already here...？</t>
+          <t>What kind of reaction would I get if I stepped out
+and said, 'Actually, I'm already here...?'</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -11346,8 +11350,8 @@
       </c>
       <c r="B708" s="1" t="inlineStr">
         <is>
-          <t>You might see a level of fluster never seen normally,
-but getting scolded is inevitable.</t>
+          <t>I might get to see Rurichiyo-chan more flustered than
+usual, but I'd inevitably get scolded.</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -11377,7 +11381,7 @@
       </c>
       <c r="B710" s="1" t="inlineStr">
         <is>
-          <t>「Haa... you all wouldn't understand, right...？」</t>
+          <t>"Sigh... they wouldn't understand, would they...?"</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -11392,8 +11396,8 @@
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>...For Rurichiyo-chan, peeing outdoors seems to be a
-pretty high hurdle.</t>
+          <t>...Peeing outdoors seems to be a pretty big hurdle
+for Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -11469,7 +11473,7 @@
       </c>
       <c r="B716" s="1" t="inlineStr">
         <is>
-          <t>Has she decided to pee secretly from everyone？</t>
+          <t>Has she decided to pee in secret?</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11499,7 +11503,7 @@
       </c>
       <c r="B718" s="1" t="inlineStr">
         <is>
-          <t>「...huh, ugh...」</t>
+          <t>「...hm...uh...」</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -11529,7 +11533,7 @@
       </c>
       <c r="B720" s="1" t="inlineStr">
         <is>
-          <t>「...huh, hmm... the grass feels a bit ticklish,
+          <t>「...ah... phew... the grass feels a bit ticklish,
 doesn't it...?」</t>
         </is>
       </c>
@@ -11575,7 +11579,7 @@
       </c>
       <c r="B723" s="1" t="inlineStr">
         <is>
-          <t>...It seems she still can't decide.</t>
+          <t>...It seems she still can't make up her mind.</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -11590,9 +11594,9 @@
       </c>
       <c r="B724" s="1" t="inlineStr">
         <is>
-          <t>Also, with her crotch exposed as she crouches, she
-seems to be very sensitive to the sway of the grass
-on the ground.</t>
+          <t>Also, because she's crouched with the area between
+her legs exposed, she seems unusually sensitive to
+the swaying of the grass beneath her.</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -11622,7 +11626,7 @@
       </c>
       <c r="B726" s="1" t="inlineStr">
         <is>
-          <t>「Haa... nngh~~！」</t>
+          <t>"Phew... nngh~~!"</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -11637,7 +11641,7 @@
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan starts to strain quietly.</t>
+          <t>Rurichiyo-chan began to strain slightly.</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -11667,7 +11671,7 @@
       </c>
       <c r="B729" s="1" t="inlineStr">
         <is>
-          <t>Rustle...！</t>
+          <t>Rustle...!</t>
         </is>
       </c>
       <c r="C729" t="n">
@@ -11757,7 +11761,7 @@
       </c>
       <c r="B735" s="1" t="inlineStr">
         <is>
-          <t>Not at my feet... it was somewhere else.</t>
+          <t>Not at my feet... somewhere else.</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -11804,7 +11808,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>「W-what, wha-what…………huh！？」</t>
+          <t>「W-w-what...!?」</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -11834,7 +11838,7 @@
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>It looked like she saw something—.</t>
+          <t>She seemed to have seen something—.</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -11864,7 +11868,7 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>「Nooooh！ It's a biiig mouse~！」</t>
+          <t>Eeeek! It's a biiig mouse~!</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -11894,8 +11898,7 @@
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>Was the thing that made the sound earlier that weasel
-from before？</t>
+          <t>Was that the weasel from earlier?</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -11910,8 +11913,8 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>I frantically scanned around and saw a weasel darting
-through.</t>
+          <t>I frantically looked around and saw a weasel dart
+past.</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -11926,8 +11929,8 @@
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
-          <t>But that was only for a moment; it quickly melted
-into the tree shadows and ran off.</t>
+          <t>But that was only for a moment; it quickly slipped
+into the shade of the trees and ran off.</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -11972,9 +11975,9 @@
       </c>
       <c r="B749" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan screamed, but she was crouched down
-with her panties lowered, so there was nothing she
-could do.</t>
+          <t>Rurichiyo-chan screamed, but she was crouching with
+her panties pulled down, so there was nothing I could
+do.</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -12005,8 +12008,8 @@
       </c>
       <c r="B751" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it, she did say she was bad with
-weasels...</t>
+          <t>Come to think of it, Rurichiyo-chan did say she was
+afraid of weasels...</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -12036,7 +12039,7 @@
       </c>
       <c r="B753" s="1" t="inlineStr">
         <is>
-          <t>「Don't come near me… go away, please~！」</t>
+          <t>「Don't come here… please go over there~！」</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -12051,8 +12054,8 @@
       </c>
       <c r="B754" s="1" t="inlineStr">
         <is>
-          <t>It's already gone, but being unable to move and
-scared like that had thrown her into a panic.</t>
+          <t>It's already gone, but she seems to be panicking —
+she was startled while unable to move.</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -12067,7 +12070,7 @@
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t>Damn... there's no choice！</t>
+          <t>Ugh... I have no choice!</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -12159,7 +12162,7 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's eyes opened even wider.</t>
+          <t>Rurichiyo-chan's eyes opened wide.</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -12204,7 +12207,8 @@
       </c>
       <c r="B764" s="1" t="inlineStr">
         <is>
-          <t>Relief washed over Rurichiyo-chan's face all at once.</t>
+          <t>A look of relief suddenly filled Rurichiyo-chan's
+eyes.</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -12326,8 +12330,9 @@
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>Even though I calmed the weasel down after it was
-startled, I can tell Rurichiyo-chan is embarrassed.</t>
+          <t>Even though I had managed to calm her after she was
+startled by the weasel, I could tell Rurichiyo-chan
+was embarrassed.</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -12343,7 +12348,7 @@
       <c r="B773" s="1" t="inlineStr">
         <is>
           <t>Precisely because I understand, I don't know what to
-say or how to support her...</t>
+say to comfort her...</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -12419,8 +12424,8 @@
       </c>
       <c r="B778" s="1" t="inlineStr">
         <is>
-          <t>But despite what I was thinking, my mouth just
-slipped...</t>
+          <t>But despite my better judgment, the words just
+slipped out...</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -12450,7 +12455,7 @@
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>「…u, uuh… uuuuh…！」</t>
+          <t>「…uh, uuh… uuuuh…！」</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -12465,8 +12470,9 @@
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>Her eyes, which had changed from surprise to relief,
-were now dyed with embarrassment...</t>
+          <t>Rurichiyo-chan's eyes, which had changed from
+surprise to relief, were now tinged with
+embarrassment...</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -12544,7 +12550,7 @@
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>...Thinking that, it was already too late.</t>
+          <t>Even as I thought that, it was already too late.</t>
         </is>
       </c>
       <c r="C786" t="n">
@@ -12574,7 +12580,7 @@
       </c>
       <c r="B788" s="1" t="inlineStr">
         <is>
-          <t>「U-uh, uh… nngh, nnnghh~~…」</t>
+          <t>「U-uh, uuh... nngh, nnnghh~~...」</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -12589,8 +12595,8 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan looked like she was about to cry, but
-her expression was complicated.</t>
+          <t>Rurichiyo-chan looked on the verge of tears, but her
+expression was conflicted.</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12605,8 +12611,8 @@
       </c>
       <c r="B790" s="1" t="inlineStr">
         <is>
-          <t>…It's a bit late to say it now, but I'm going to
-leave Rurichiyo-chan alone.</t>
+          <t>It's a bit late to say this, but I'll leave
+Rurichiyo-chan alone.</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -12636,7 +12642,7 @@
       </c>
       <c r="B792" s="1" t="inlineStr">
         <is>
-          <t>「Ah... sorry, should I go over there... then？」</t>
+          <t>"Ah... sorry. I'll go over there... okay?"</t>
         </is>
       </c>
       <c r="C792" t="n">
@@ -12666,7 +12672,7 @@
       </c>
       <c r="B794" s="1" t="inlineStr">
         <is>
-          <t>「Huff, ugh... nn, nnn~~~...！」</t>
+          <t>「U-uh, uuh... nngh, nnnghh~~~...！」</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -12681,7 +12687,7 @@
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>Shaa~~~...</t>
+          <t>Shhhhh...</t>
         </is>
       </c>
       <c r="C795" t="n">
@@ -12696,7 +12702,8 @@
       </c>
       <c r="B796" s="1" t="inlineStr">
         <is>
-          <t>...She starts peeing right in front of me...</t>
+          <t>...Rurichiyo-chan starts peeing right in front of
+me...</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -12742,7 +12749,7 @@
       </c>
       <c r="B799" s="1" t="inlineStr">
         <is>
-          <t>「N-no… please don't look！」</t>
+          <t>"N-no... please don't look at me!"</t>
         </is>
       </c>
       <c r="C799" t="n">
@@ -12757,8 +12764,8 @@
       </c>
       <c r="B800" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan says that, but I couldn't take my eyes
-away.</t>
+          <t>Rurichiyo-chan said that, but I couldn't take my eyes
+off her.</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -12773,7 +12780,7 @@
       </c>
       <c r="B801" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's peeing…！</t>
+          <t>Rurichiyo-chan is peeing...!</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -12788,8 +12795,8 @@
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
-          <t>No way, having her pee at this timing must be the
-worst for Rurichiyo-chan.</t>
+          <t>Of all times, peeing right now must be the worst
+thing for Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -12804,8 +12811,8 @@
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>But outdoor peeing by Rurichiyo-chan is such a rare
-thing that there's no way I'd pass up seeing it…！</t>
+          <t>But Rurichiyo-chan peeing outdoors is such a rarity —
+it's not something you'd ever see, even by chance…！</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -12866,10 +12873,9 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>The contrast between her cheeks flushed with shame
-and her half-closed, blissful eyes from the urge to
-urinate tells the whole story of Rurichiyo-chan's
-state.</t>
+          <t>The contrast between her shame-flushed cheeks and the
+dreamy, entranced look in her eyes from the urge to
+urinate says everything about Rurichiyo-chan's state.</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -12884,8 +12890,8 @@
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>On top of that, the smell of pee overflowing from
-between her legs tickles my nostrils…</t>
+          <t>On top of that, the smell of pee spilling from
+between Rurichiyo-chan's legs tickles my nostrils…</t>
         </is>
       </c>
       <c r="C808" t="n">
@@ -12900,8 +12906,8 @@
       </c>
       <c r="B809" s="1" t="inlineStr">
         <is>
-          <t>Right now I'm filled with Rurichiyo-chan in sight,
-sound, and even smell.</t>
+          <t>Right now my sight, hearing, and even my sense of
+smell are filled with Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C809" t="n">
@@ -12931,7 +12937,7 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>「Ah… nn, nn！ Nn…！」</t>
+          <t>「Ah... nngh, nngh! Nn...!」</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -12946,8 +12952,8 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan finishes peeing while making cute
-little moans.</t>
+          <t>Rurichiyo-chan lets out cute little moans as she
+finishes peeing.</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -12962,8 +12968,8 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>She's embarrassed, but she probably has no choice but
-to do it now.</t>
+          <t>Rurichiyo-chan is embarrassed, but she probably has
+no choice but to go through with it.</t>
         </is>
       </c>
       <c r="C813" t="n">
@@ -12993,7 +12999,7 @@
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>「Phew… ugh…」</t>
+          <t>「Phew... uuh...」</t>
         </is>
       </c>
       <c r="C815" t="n">
@@ -13008,7 +13014,7 @@
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
-          <t>Then, with a small groan, the peeing stops.</t>
+          <t>Then, with a small moan, the peeing stops.</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -13038,9 +13044,9 @@
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
-          <t>If she felt shame about peeing outside but still had
-to do it, that means she must've been holding it in
-quite a lot.</t>
+          <t>If Rurichiyo-chan felt ashamed about peeing outside
+but was forced to, that means she must have been
+holding it in for quite a long time.</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -13055,8 +13061,8 @@
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
-          <t>But even so... ah, even so, I got seen by me, and on
-top of that I even peed...！</t>
+          <t>But even so... ah, even so, she was seen by me, and
+on top of that she even peed...!</t>
         </is>
       </c>
       <c r="C819" t="n">
@@ -13071,7 +13077,7 @@
       </c>
       <c r="B820" s="1" t="inlineStr">
         <is>
-          <t>That expression again, it was just so cute...！</t>
+          <t>That expression of hers was so unbelievably cute...!</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -13131,7 +13137,7 @@
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>「...........Hah!？!」</t>
+          <t>「……Huh!?」</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -13146,8 +13152,8 @@
       </c>
       <c r="B825" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's reaction was far too cute, and my
-thoughts started looping endlessly.</t>
+          <t>Rurichiyo-chan's reaction was just too cute, and my
+thoughts began to spiral into an endless chain.</t>
         </is>
       </c>
       <c r="C825" t="n">
@@ -13162,8 +13168,8 @@
       </c>
       <c r="B826" s="1" t="inlineStr">
         <is>
-          <t>In that moment, Rurichiyo-chan came to her senses
-first.</t>
+          <t>Meanwhile, Rurichiyo-chan was the first to come to
+her senses.</t>
         </is>
       </c>
       <c r="C826" t="n">
@@ -13208,9 +13214,9 @@
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan hurriedly stood up and pulled up her
-panties, looking at me with eyes on the verge of
-tears.</t>
+          <t>Rurichiyo-chan hurriedly stood up and pulled her
+panties back up, staring at me with eyes on the verge
+of tears.</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -13240,7 +13246,7 @@
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah... um, hey？」</t>
+          <t>「Ah... ah... um... about that?」</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -13363,7 +13369,7 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>「Ah, welcome back~！ So you found Ruri-chan~」</t>
+          <t>"Ah, welcome back~! You found Ruri-chan, huh~"</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -13409,7 +13415,7 @@
       </c>
       <c r="B842" s="1" t="inlineStr">
         <is>
-          <t>「Ah, yeah... Rurichiyo-chan was here...」</t>
+          <t>"Ah, yeah... Rurichiyo-chan's here..."</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -13439,7 +13445,7 @@
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
-          <t>「Ruri-chan, what were you doing？」</t>
+          <t>"Ruri-chan, what were you doing?"</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -13484,9 +13490,9 @@
       </c>
       <c r="B847" s="1" t="inlineStr">
         <is>
-          <t>I gave a nervous smile to avoid having the earlier
-situation asked about, but Rurichiyo-chan pouted and
-turned away.</t>
+          <t>I forced a polite smile so I wouldn't be asked about
+what had just happened, but Rurichiyo-chan was
+sulking.</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -13638,8 +13644,7 @@
       </c>
       <c r="B857" s="1" t="inlineStr">
         <is>
-          <t>「N-no, I didn't do anything！？ Hey, right,
-Rurichiyo-chan？」</t>
+          <t>「N-no, I didn't do anything! Right, Rurichiyo-chan?」</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -13669,7 +13674,7 @@
       </c>
       <c r="B859" s="1" t="inlineStr">
         <is>
-          <t>「Um... I didn't do anything...！」</t>
+          <t>"No... I didn't do anything...!"</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -13684,8 +13689,7 @@
       </c>
       <c r="B860" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan said, sticking out her lips as she
-spoke.</t>
+          <t>Rurichiyo-chan said sharply, lips pursed.</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -13700,9 +13704,9 @@
       </c>
       <c r="B861" s="1" t="inlineStr">
         <is>
-          <t>In truth, my hands didn't touch her, so my
-explanation is accurate... but the situation is only
-getting worse.</t>
+          <t>I didn't actually touch her, so my explanation of the
+situation is correct... but things are only getting
+worse.</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -13732,7 +13736,7 @@
       </c>
       <c r="B863" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan~？ Be honest, okay？」</t>
+          <t>"Niini~? Tell me honestly, okay?"</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -13747,8 +13751,8 @@
       </c>
       <c r="B864" s="1" t="inlineStr">
         <is>
-          <t>Maybe because Rurichiyo-chan is sulking, Miru-chan
-pressed me more maturely.</t>
+          <t>Maybe because Rurichiyo-chan was pouting, Miru-chan
+grilled me in a more grown-up way.</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -13763,8 +13767,8 @@
       </c>
       <c r="B865" s="1" t="inlineStr">
         <is>
-          <t>When someone else starts panicking, it kind of makes
-her end up feeling calm…</t>
+          <t>It's kind of like that feeling where, when someone
+else panics, I end up staying calm instead...</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -13810,7 +13814,7 @@
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
-          <t>「No, really, I didn't do anything...」</t>
+          <t>No, really, I didn't do anything...</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -13871,7 +13875,7 @@
       </c>
       <c r="B872" s="1" t="inlineStr">
         <is>
-          <t>「Well, that's because there are various reasons... ？」</t>
+          <t>"Well, that's because there are various reasons...?"</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -13886,8 +13890,8 @@
       </c>
       <c r="B873" s="1" t="inlineStr">
         <is>
-          <t>Aside from any horny intentions, I do have a
-legitimate reason... but I can't say it.</t>
+          <t>Aside from lewd motives, I have a legitimate
+justification... but I can't say it.</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13963,8 +13967,8 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei and Rurichiyo-chan might have had
-things they found hard to tell others...！」</t>
+          <t>Janitor-sensei and Rurichiyo-chan might have had
+things they found hard to tell others...！</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -14010,7 +14014,7 @@
       </c>
       <c r="B881" s="1" t="inlineStr">
         <is>
-          <t>「Things that are hard to tell people... like what？」</t>
+          <t>Things that are hard to tell people... like what?</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -14040,7 +14044,7 @@
       </c>
       <c r="B883" s="1" t="inlineStr">
         <is>
-          <t>「A~ ya~ shii~...！」</t>
+          <t>「Ah~ ya~ Shii~……！」</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -14055,8 +14059,8 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>As expected, Rin-chan and Miru-chan seized on the end
-of the phrase.</t>
+          <t>As expected, Rin-chan and Miru-chan seized on my
+choice of words.</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -14086,9 +14090,9 @@
       </c>
       <c r="B886" s="1" t="inlineStr">
         <is>
-          <t>「...If someone tells you something that's hard to
-say, the adult move is not to pry any
-further...right, Nono-chan？」</t>
+          <t>"...If someone says it's something that's hard to
+tell others, the adult thing to do is not to press
+them for more...right, Nono-chan?"</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -14118,7 +14122,7 @@
       </c>
       <c r="B888" s="1" t="inlineStr">
         <is>
-          <t>「W-well...yeah...」</t>
+          <t>「W-well... um... yes...」</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -14149,7 +14153,7 @@
       </c>
       <c r="B890" s="1" t="inlineStr">
         <is>
-          <t>It seemed she was also distracted by Miru-chan and
+          <t>Apparently I was also distracted by Miru-chan and
 Rin-chan giving me suspicious looks.</t>
         </is>
       </c>
@@ -14211,7 +14215,7 @@
       </c>
       <c r="B894" s="1" t="inlineStr">
         <is>
-          <t>「Ah...uu...」</t>
+          <t>「Ah... ugh...」</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -14242,7 +14246,8 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>But her eyes had shifted a bit from angry-mode.</t>
+          <t>But the expression in her eyes had shifted slightly
+out of angry mode.</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -14272,8 +14277,8 @@
       </c>
       <c r="B898" s="1" t="inlineStr">
         <is>
-          <t>Everyone went into angry mode, so have they actually
-calmed down again？</t>
+          <t>Now that everyone's gone into angry mode, have I, on
+the other hand, calmed down again?</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -14424,7 +14429,7 @@
       </c>
       <c r="B908" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ That's the Itachi from earlier！」</t>
+          <t>「Ah! It's that Itachi-san from earlier!」</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -14454,7 +14459,7 @@
       </c>
       <c r="B910" s="1" t="inlineStr">
         <is>
-          <t>「The Itachi came back...」</t>
+          <t>Itachi-san came back...</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -14486,7 +14491,7 @@
       </c>
       <c r="B912" s="1" t="inlineStr">
         <is>
-          <t>You came back again...？</t>
+          <t>Itachi-san came back again...?</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -14501,7 +14506,7 @@
       </c>
       <c r="B913" s="1" t="inlineStr">
         <is>
-          <t>...So then, Rurichiyo-chan...？</t>
+          <t>...Then, Rurichiyo-chan...?</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -14531,7 +14536,7 @@
       </c>
       <c r="B915" s="1" t="inlineStr">
         <is>
-          <t>「...No, wait, no...！」</t>
+          <t>「N-no, no...!」</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -14577,7 +14582,7 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>「It's a big mouse~~~！！」</t>
+          <t>"It's a huge mouse!!"</t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -14622,7 +14627,7 @@
       </c>
       <c r="B921" s="1" t="inlineStr">
         <is>
-          <t>「Hey, Rurichiyo-chan！ Wait！」</t>
+          <t>「Hey, Rurichiyo-chan! Wait!」</t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -14668,7 +14673,7 @@
       </c>
       <c r="B924" s="1" t="inlineStr">
         <is>
-          <t>「Oh, and just so you know, it's that thing's fault！」</t>
+          <t>「Ah, just so you know, it's that weasel's fault!」</t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -14699,9 +14704,8 @@
       </c>
       <c r="B926" s="1" t="inlineStr">
         <is>
-          <t>They probably had no idea what I was talking about,
-but maybe things will be different when we get back
-next time...</t>
+          <t>They probably don't know what's going on, but maybe
+things will be different by the time we come back...</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -14795,7 +14799,7 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>Damn... did it curse me or something？</t>
+          <t>Damn... did that weasel put a curse on me?</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -14810,8 +14814,8 @@
       </c>
       <c r="B933" s="1" t="inlineStr">
         <is>
-          <t>Even the treasures my past self gave me were
-confiscated...</t>
+          <t>Even the treasures she'd been given by her past self
+were confiscated...</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -14841,8 +14845,8 @@
       </c>
       <c r="B935" s="1" t="inlineStr">
         <is>
-          <t>That's it！ While I have the chance, I'll go retrieve
-my bible.</t>
+          <t>That's it! I'll go retrieve my bible while I have the
+chance.</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -14857,8 +14861,8 @@
       </c>
       <c r="B936" s="1" t="inlineStr">
         <is>
-          <t>I'll go talk to Nono-chan face-to-face and get it
-back！</t>
+          <t>I'll go and confront Nono-chan in person and get it
+back!</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -14889,7 +14893,7 @@
       </c>
       <c r="B938" s="1" t="inlineStr">
         <is>
-          <t>...Okay, how should I start this？</t>
+          <t>Now then... how should I bring this up?</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -14904,7 +14908,7 @@
       </c>
       <c r="B939" s="1" t="inlineStr">
         <is>
-          <t>After all, it's a dirty book.</t>
+          <t>After all, it's an erotic book.</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -14919,7 +14923,7 @@
       </c>
       <c r="B940" s="1" t="inlineStr">
         <is>
-          <t>...No, it's the guilt that's the problem.</t>
+          <t>...No — it's because I feel guilty.</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -14934,7 +14938,7 @@
       </c>
       <c r="B941" s="1" t="inlineStr">
         <is>
-          <t>Even if it's a dirty book, it's mine.</t>
+          <t>Even if it's an erotic book, it's mine.</t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -14996,8 +15000,7 @@
       </c>
       <c r="B945" s="1" t="inlineStr">
         <is>
-          <t>Before I knocked, I ran through simulations in my
-head.</t>
+          <t>Before I knocked, I ran the scenario through my head.</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -15012,8 +15015,8 @@
       </c>
       <c r="B946" s="1" t="inlineStr">
         <is>
-          <t>Like whether to blurt it out right away, or hint
-around so they'd return it...</t>
+          <t>Whether to blurt it out right away, or to ask her
+indirectly to give it back...</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -15043,8 +15046,8 @@
       </c>
       <c r="B948" s="1" t="inlineStr">
         <is>
-          <t>Ugh, trying to get a dirty book back is even harder
-to bring up if there are two girls...</t>
+          <t>Ugh, it's even harder to ask for my erotic book back
+when there are two girls around...</t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -15136,8 +15139,7 @@
       </c>
       <c r="B954" s="1" t="inlineStr">
         <is>
-          <t>I quietly peek through the gap to look inside the
-door—.</t>
+          <t>I quietly peered through the crack in the door.</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -15212,7 +15214,7 @@
       </c>
       <c r="B959" s="1" t="inlineStr">
         <is>
-          <t>Uah…… they're all gathered and reading…….</t>
+          <t>Whoa... They're all gathered and reading it...</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -15227,8 +15229,8 @@
       </c>
       <c r="B960" s="1" t="inlineStr">
         <is>
-          <t>They're so absorbed they didn't notice the door open
-at all…… they're really into it…….</t>
+          <t>They're so engrossed in reading that not a single
+person even noticed the door opening…</t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -15258,7 +15260,7 @@
       </c>
       <c r="B962" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaa…………」</t>
+          <t>「Yaaawn…………」</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -15288,7 +15290,7 @@
       </c>
       <c r="B964" s="1" t="inlineStr">
         <is>
-          <t>「...！  ...」</t>
+          <t>「...! ...」</t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -15318,7 +15320,7 @@
       </c>
       <c r="B966" s="1" t="inlineStr">
         <is>
-          <t>「Haa……, mmm…………」</t>
+          <t>「Haa…… mmm…………」</t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -15348,7 +15350,7 @@
       </c>
       <c r="B968" s="1" t="inlineStr">
         <is>
-          <t>「Muu…......uu……」</t>
+          <t>「Mmm... uuu...」</t>
         </is>
       </c>
       <c r="C968" t="n">
@@ -15363,7 +15365,7 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>Everyone let out suppressed breaths as they read.</t>
+          <t>Everyone let out stifled breaths as they read.</t>
         </is>
       </c>
       <c r="C969" t="n">
@@ -15378,8 +15380,8 @@
       </c>
       <c r="B970" s="1" t="inlineStr">
         <is>
-          <t>They were curious, but seeing it must have
-embarrassed them.</t>
+          <t>They were curious, but they probably got embarrassed
+when they looked.</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -15425,8 +15427,9 @@
       </c>
       <c r="B973" s="1" t="inlineStr">
         <is>
-          <t>Knowing my first porn was being seen by everyone made
-me feel like my sexual tastes were exposed.</t>
+          <t>Having everyone see the first thing I used as
+masturbation material made me feel like my kinks were
+being exposed.</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -15441,8 +15444,9 @@
       </c>
       <c r="B974" s="1" t="inlineStr">
         <is>
-          <t>And they were the smaller ones watching… it made me
-feel really wrong…</t>
+          <t>On top of that, being watched by the little ones...
+made me feel like I was doing something really
+wrong...</t>
         </is>
       </c>
       <c r="C974" t="n">
@@ -15457,8 +15461,8 @@
       </c>
       <c r="B975" s="1" t="inlineStr">
         <is>
-          <t>It was the same shameful, unbearable feeling as when
-I showed my penis to everyone.</t>
+          <t>It felt just as shameful and wrong as when I showed
+my penis to everyone.</t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -15488,7 +15492,7 @@
       </c>
       <c r="B977" s="1" t="inlineStr">
         <is>
-          <t>「Wha... so this is what ‘sex’ is...？」</t>
+          <t>"Eh... so this is what 'ecchi' is...?"</t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -15550,7 +15554,7 @@
       </c>
       <c r="B981" s="1" t="inlineStr">
         <is>
-          <t>「Th-this is... perfect as sex-ed material, isn't it?」</t>
+          <t>Th-this is... perfect as sex-ed material, isn't it?</t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -15581,9 +15585,8 @@
       </c>
       <c r="B983" s="1" t="inlineStr">
         <is>
-          <t>But even saying that, there's a kind of childlike
-coyness, like she's trying to hide that she's
-interested.</t>
+          <t>But even saying that, you can see a childlike
+innocence, as if she's trying to hide her interest.</t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -15643,8 +15646,8 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>Even when there are only girls around, she still
-seems embarrassed.</t>
+          <t>Even when there are only girls present, they still
+seem embarrassed.</t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -15674,7 +15677,7 @@
       </c>
       <c r="B989" s="1" t="inlineStr">
         <is>
-          <t>「‘Shasee’—so you put it here on a girl, huh…」</t>
+          <t>「'Shasee'—so you do that on a girl's 'there'...」</t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -15689,8 +15692,8 @@
       </c>
       <c r="B990" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan's face was bright red, yet she was
-showing a surprisingly earnest side.</t>
+          <t>Rurichiyo-chan's face was bright red, yet she showed
+a very earnest side.</t>
         </is>
       </c>
       <c r="C990" t="n">
@@ -15721,8 +15724,8 @@
       </c>
       <c r="B992" s="1" t="inlineStr">
         <is>
-          <t>She said she saw an ejaculation, but that she wasn't
-taught about the real thing…….</t>
+          <t>She said she'd seen someone ejaculate, but she'd
+never been taught about the actual act...</t>
         </is>
       </c>
       <c r="C992" t="n">
@@ -15767,8 +15770,8 @@
       </c>
       <c r="B995" s="1" t="inlineStr">
         <is>
-          <t>Ah……seeing a girl with sexual knowledge fills me with
-such complicated feelings…….</t>
+          <t>Ah... seeing girls with sexual knowledge makes me
+feel so conflicted...</t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -15783,8 +15786,9 @@
       </c>
       <c r="B996" s="1" t="inlineStr">
         <is>
-          <t>Part of me wants to say congratulations, and part of
-me wants her to remain clueless.</t>
+          <t>Part of me wants to say 'congratulations,' but
+another part wants the girls to remain completely
+unaware.</t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -15799,7 +15803,7 @@
       </c>
       <c r="B997" s="1" t="inlineStr">
         <is>
-          <t>That's probably a guy's ego, though…….</t>
+          <t>That's probably a guy's ego, though...</t>
         </is>
       </c>
       <c r="C997" t="n">
@@ -15815,7 +15819,7 @@
       <c r="B998" s="1" t="inlineStr">
         <is>
           <t>But if it's going to happen anyway, I want to teach
-her hands-on……！</t>
+them hands-on...!</t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -15845,7 +15849,7 @@
       </c>
       <c r="B1000" s="1" t="inlineStr">
         <is>
-          <t>「……But, does it really feel good？」</t>
+          <t>"…But does it really feel that good?"</t>
         </is>
       </c>
       <c r="C1000" t="n">
@@ -15875,8 +15879,8 @@
       </c>
       <c r="B1002" s="1" t="inlineStr">
         <is>
-          <t>For someone who was so embarrassed, she hit the nail
-on the head.</t>
+          <t>Despite appearing embarrassed, she accurately grasped
+the key points.</t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -15937,7 +15941,8 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>「Well... she kept saying, 'kimoiii, kimoiii.'」</t>
+          <t>Well... she kept saying, 'It feels so good, it feels
+so good.'</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -15967,8 +15972,8 @@
       </c>
       <c r="B1008" s="1" t="inlineStr">
         <is>
-          <t>「kimochiii… does it mean the same thing as ‘feels
-good’？」</t>
+          <t>Feels gooood... does that mean the same thing as
+'feels good'?</t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -16013,8 +16018,8 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's remark was the trigger, and everyone began
-to take a step forward.</t>
+          <t>Rin-chan's comment prompted everyone to take a step
+forward.</t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -16044,8 +16049,7 @@
       </c>
       <c r="B1013" s="1" t="inlineStr">
         <is>
-          <t>「Onii-chan, you looked like you were feeling good…
-right…？」</t>
+          <t>Onii-chan seemed to be enjoying it... didn't he?</t>
         </is>
       </c>
       <c r="C1013" t="n">
@@ -16075,7 +16079,7 @@
       </c>
       <c r="B1015" s="1" t="inlineStr">
         <is>
-          <t>「She said that, but she looked a little miserable.」</t>
+          <t>She said that, but she seemed to be in a bit of pain.</t>
         </is>
       </c>
       <c r="C1015" t="n">
@@ -16105,7 +16109,7 @@
       </c>
       <c r="B1017" s="1" t="inlineStr">
         <is>
-          <t>「I think the guy in the manga looked like I was in
+          <t>「I think the guy in the manga looked like he was in
 pain...」</t>
         </is>
       </c>
@@ -16136,7 +16140,7 @@
       </c>
       <c r="B1019" s="1" t="inlineStr">
         <is>
-          <t>「I see... I wonder, Nono-chan？」</t>
+          <t>Oh... what do you think, Nono-chan?</t>
         </is>
       </c>
       <c r="C1019" t="n">
@@ -16151,7 +16155,7 @@
       </c>
       <c r="B1020" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan brings up the topic of nature with
+          <t>Miru-chan naturally steers the conversation toward
 Nono-chan.</t>
         </is>
       </c>
@@ -16167,7 +16171,7 @@
       </c>
       <c r="B1021" s="1" t="inlineStr">
         <is>
-          <t>Did you think the teacher would answer？</t>
+          <t>Did you think Sensei would answer?</t>
         </is>
       </c>
       <c r="C1021" t="n">
@@ -16258,8 +16262,8 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>「...Anyway, I think right now we have no choice but
-to examine a lot more cases.」</t>
+          <t>「...In any case, for now I think we have no choice
+but to examine many more cases.」</t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -16289,7 +16293,7 @@
       </c>
       <c r="B1029" s="1" t="inlineStr">
         <is>
-          <t>「...jiree wo kensho？」</t>
+          <t>「...Examine the cases?」</t>
         </is>
       </c>
       <c r="C1029" t="n">
@@ -16319,8 +16323,7 @@
       </c>
       <c r="B1031" s="1" t="inlineStr">
         <is>
-          <t>「Yes, in other words...let's take a look at the next
-manga...！」</t>
+          <t>Okay, then... let's take a look at the next manga...!</t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -16365,8 +16368,8 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>When Nono-chan said it all solemnly, everyone else
-made throaty sounds in unison.</t>
+          <t>When Nono-chan spoke, putting on a serious air, the
+others all swallowed in unison.</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -16396,7 +16399,7 @@
       </c>
       <c r="B1036" s="1" t="inlineStr">
         <is>
-          <t>「Well then...here we go...！」</t>
+          <t>「All right... here we go...！」</t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -16427,8 +16430,7 @@
       </c>
       <c r="B1038" s="1" t="inlineStr">
         <is>
-          <t>Did I become unable to look away... is that what I
-should say？</t>
+          <t>Should I say I couldn't take my eyes off it...?</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -16443,9 +16445,9 @@
       </c>
       <c r="B1039" s="1" t="inlineStr">
         <is>
-          <t>It looked like we’d finished a manga and were trading
-impressions, but I guess they’ll stay quiet for a
-while...</t>
+          <t>It seemed we’d finished reading a manga and were
+exchanging impressions, but would we remain silent
+for a while...?</t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -16460,7 +16462,7 @@
       </c>
       <c r="B1040" s="1" t="inlineStr">
         <is>
-          <t>This is... there's no way I can butt in.</t>
+          <t>There's no way I can say anything about this.</t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -16475,7 +16477,7 @@
       </c>
       <c r="B1041" s="1" t="inlineStr">
         <is>
-          <t>I'll leave them alone for a bit and deal with it
+          <t>I'll leave it alone for a while and collect it
 later...</t>
         </is>
       </c>
@@ -16569,8 +16571,8 @@
       </c>
       <c r="B1047" s="1" t="inlineStr">
         <is>
-          <t>She called out loudly, then headed back to the living
-room.</t>
+          <t>I called out loudly, then immediately went back to
+the living room.</t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -16585,8 +16587,8 @@
       </c>
       <c r="B1048" s="1" t="inlineStr">
         <is>
-          <t>I want the hot stuff to be ready between calling them
-and them actually coming.</t>
+          <t>I want the hot dishes to be ready between when I call
+everyone and when they arrive.</t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -16662,7 +16664,7 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>「Everyone~！ Dinner's ready~！！」</t>
+          <t>"Hey everyone—dinner's ready~!!"</t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -16677,8 +16679,8 @@
       </c>
       <c r="B1054" s="1" t="inlineStr">
         <is>
-          <t>She called out loudly again, and this time everyone
-came out together.</t>
+          <t>I called out loudly one more time, and this time
+everyone came out together.</t>
         </is>
       </c>
       <c r="C1054" t="n">
@@ -16693,7 +16695,7 @@
       </c>
       <c r="B1055" s="1" t="inlineStr">
         <is>
-          <t>Maybe they were reading the whole time...？</t>
+          <t>Maybe they'd been reading the whole time...?</t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -16723,7 +16725,7 @@
       </c>
       <c r="B1057" s="1" t="inlineStr">
         <is>
-          <t>「...Dinner's ready, okay？」</t>
+          <t>「...Dinner's ready?」</t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -16753,7 +16755,7 @@
       </c>
       <c r="B1059" s="1" t="inlineStr">
         <is>
-          <t>「Ah... y-yes」</t>
+          <t>「Ah... y-yes~」</t>
         </is>
       </c>
       <c r="C1059" t="n">
@@ -16874,8 +16876,8 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan bustles about happily. Nono-chan
-offers a polite line, but her smile is strained.</t>
+          <t>Rurichiyo-chan bustles about eagerly. Nono-chan
+offers a polite reply, but her smile is strained.</t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -16937,7 +16939,7 @@
       </c>
       <c r="B1071" s="1" t="inlineStr">
         <is>
-          <t>That left one task—time to collect Comic RO...！</t>
+          <t>That left only one task: collecting Comic RO...!</t>
         </is>
       </c>
       <c r="C1071" t="n">
@@ -16952,8 +16954,8 @@
       </c>
       <c r="B1072" s="1" t="inlineStr">
         <is>
-          <t>I couldn't recover it earlier, but this time for sure
-I want to get it back no matter what.</t>
+          <t>I couldn't collect it earlier, but this time I want
+to collect it no matter what.</t>
         </is>
       </c>
       <c r="C1072" t="n">
@@ -16968,7 +16970,7 @@
       </c>
       <c r="B1073" s="1" t="inlineStr">
         <is>
-          <t>But I have a secret plan….</t>
+          <t>However, I have a secret plan...</t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -16999,8 +17001,8 @@
       </c>
       <c r="B1075" s="1" t="inlineStr">
         <is>
-          <t>Then we should flip the fact that it’s an erotic book
-to our advantage and tease them from our side.</t>
+          <t>I should use the fact that it's an erotic book to my
+advantage and tease them.</t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -17015,8 +17017,8 @@
       </c>
       <c r="B1076" s="1" t="inlineStr">
         <is>
-          <t>So if you asked Nono-chan, "Do you want to read
-it？"...</t>
+          <t>In other words, if I said to Nono-chan, "Do you want
+to read it?..."</t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -17031,7 +17033,7 @@
       </c>
       <c r="B1077" s="1" t="inlineStr">
         <is>
-          <t>No no no no！ N-Not at all, I'll give it back！</t>
+          <t>N-no! That's not it — I'll give it back!</t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -17062,7 +17064,7 @@
       </c>
       <c r="B1079" s="1" t="inlineStr">
         <is>
-          <t>I guess so.</t>
+          <t>I'm sure.</t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -17170,7 +17172,7 @@
       </c>
       <c r="B1086" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chaaaan, are you there？」</t>
+          <t>「Nono-chan, are you there?」</t>
         </is>
       </c>
       <c r="C1086" t="n">
@@ -17321,8 +17323,8 @@
       </c>
       <c r="B1096" s="1" t="inlineStr">
         <is>
-          <t>What should I do… I don't want to just back off and
-say there's no answer.</t>
+          <t>What should I do… I don't want to just give up and
+walk away because there's no answer.</t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -17337,7 +17339,7 @@
       </c>
       <c r="B1097" s="1" t="inlineStr">
         <is>
-          <t>Unable to give up, I felt bad but opened the door.</t>
+          <t>Unable to give up, I opened the door, feeling guilty.</t>
         </is>
       </c>
       <c r="C1097" t="n">
@@ -17398,7 +17400,8 @@
       </c>
       <c r="B1101" s="1" t="inlineStr">
         <is>
-          <t>Not just Nono-chan, Rurichiyo-chan was gone too.</t>
+          <t>Not only Nono-chan, but Rurichiyo-chan isn't here
+either.</t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -17475,7 +17478,7 @@
       </c>
       <c r="B1106" s="1" t="inlineStr">
         <is>
-          <t>Maybe they're all reading it together again…？</t>
+          <t>I wonder if they're all reading it together again...</t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -17490,7 +17493,7 @@
       </c>
       <c r="B1107" s="1" t="inlineStr">
         <is>
-          <t>I wonder if I'm in Miru-chan and Rin-chan's room？</t>
+          <t>I wonder if they're in Miru-chan and Rin-chan's room?</t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -17505,8 +17508,8 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>…But, do people really read erotic books together
-over and over？</t>
+          <t>But would they really all be reading an erotic book
+over and over?</t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -17521,7 +17524,7 @@
       </c>
       <c r="B1109" s="1" t="inlineStr">
         <is>
-          <t>Even if it’s guys watching together, once is enough.</t>
+          <t>Even if it's just guys looking at it, once is enough.</t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -17552,7 +17555,7 @@
       </c>
       <c r="B1111" s="1" t="inlineStr">
         <is>
-          <t>If he’s a guy at that awkward age, he’ll pass it
+          <t>If they're guys at that awkward age, they'd pass it
 around to read...</t>
         </is>
       </c>
@@ -17598,7 +17601,7 @@
       </c>
       <c r="B1114" s="1" t="inlineStr">
         <is>
-          <t>A chill runs down my spine at my own imagination.</t>
+          <t>She felt a chill run down her spine at the thought.</t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -17644,7 +17647,7 @@
       </c>
       <c r="B1117" s="1" t="inlineStr">
         <is>
-          <t>No, not just anyone — in this case, the one who'd
+          <t>No, not just anyone — in this case, the person who'd
 probably have it is...</t>
         </is>
       </c>
